--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -4078,7 +4078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4301,12 +4301,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>domain_code</t>
+          <t>service_description</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>varchar(300)</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr"/>
@@ -4320,31 +4320,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>CLOSING, JOURNAL, EXPENSE, STATEMENT, CSM (파일럿 5개, 확장 가능)</t>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>업무 도메인 분류 코드(표시용)</t>
+          <t>서비스 설명(업무 목적). CON-01 §8.3 필수 항목</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>CLOSING</t>
+          <t>결산 단계별 상태 조회</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>service_type</t>
+          <t>domain_code</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>varchar(10)</t>
+          <t>varchar(30)</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
@@ -4360,29 +4360,29 @@
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>READ(조회), ACTION(실행)  ※CHECK</t>
+          <t>CLOSING, JOURNAL, EXPENSE, STATEMENT, CSM (파일럿 5개, 확장 가능)</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>서비스 성격. 등록 시 값 검증에만 사용</t>
+          <t>업무 도메인 분류 코드(표시용)</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>CLOSING</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>source_system</t>
+          <t>service_type</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>varchar(10)</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr"/>
@@ -4393,34 +4393,34 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>'IFRS17'</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>IFRS17 (Phase1 기본·고정, 확장 가능)</t>
+          <t>READ(조회), ACTION(실행)  ※CHECK</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>서비스 원천 시스템(표시용)</t>
+          <t>서비스 성격. 등록 시 값 검증에만 사용</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>IFRS17</t>
+          <t>READ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>owner_department</t>
+          <t>source_system</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>varchar(30)</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr"/>
@@ -4431,34 +4431,34 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>'IFRS17'</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>IFRS17 (Phase1 기본·고정, 확장 가능)</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>서비스 업무 책임 부서(Owner)</t>
+          <t>서비스 원천 시스템(표시용)</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>정보기술팀</t>
+          <t>IFRS17</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>active_yn</t>
+          <t>owner_department</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>char(1)</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr"/>
@@ -4469,34 +4469,34 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>'Y'</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>Y(사용), N(미사용)</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>서비스 사용 여부(N이면 신규 호출 즉시 차단) [핵심 로직]</t>
+          <t>서비스 업무 책임 부서(Owner)</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>정보기술팀</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>active_yn</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>char(1)</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr"/>
@@ -4507,34 +4507,34 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>current_timestamp</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>'Y'</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Y(사용), N(미사용)</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>최초 등록 일시(감사)</t>
+          <t>서비스 사용 여부(N이면 신규 호출 즉시 차단) [핵심 로직]</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14 09:00:00</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr"/>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>current_timestamp</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -4555,24 +4555,24 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>최초 등록자 ID(감사)</t>
+          <t>최초 등록 일시(감사)</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>E12345</t>
+          <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>varchar(30)</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>current_timestamp</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -4593,24 +4593,24 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>최종 수정 일시(감사)</t>
+          <t>최초 등록자 ID(감사)</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:00</t>
+          <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr"/>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>current_timestamp</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -4631,17 +4631,55 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
+          <t>최종 수정 일시(감사)</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>updated_by</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr"/>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
           <t>최종 수정자 ID(감사)</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4652,7 +4690,7 @@
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="A1:H1"/>

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,12 +63,30 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -87,7 +105,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -149,37 +182,43 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -546,15 +585,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -589,15 +629,20 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>사용 여부</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>목적/설명</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>주요 Key (PK)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>정의 출처</t>
         </is>
@@ -617,17 +662,22 @@
           <t>서비스 Catalog</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Business Service 마스터(서비스 존재 등록). 버전·상태 세부는 BS_SERVICE_VERSION이 담당</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
@@ -647,17 +697,22 @@
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>서비스의 버전별 상태·Schema·Timeout·구현 Bean 정의</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>service_id + version</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
@@ -677,17 +732,22 @@
           <t>입력 파라미터 정의</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>미사용(정의만)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>서비스 버전별 입력 파라미터 명세(§8.3 요청 JSON 명세)</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>service_id + version + param_name</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -707,17 +767,22 @@
           <t>서비스 역할 권한</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>서비스 호출에 필요한 허용 역할(§6.2 권한 원칙, §8.3 허용 역할)</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>service_id + role_code</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -737,17 +802,22 @@
           <t>호출 Client 등록</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>서비스를 호출하는 Client(채널) 등록(§5.2 X-Client-ID)</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -767,17 +837,22 @@
           <t>Client별 호출 허용</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Client가 호출 가능한 서비스 매핑(허용 목록)</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>client_id + service_id</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -797,17 +872,22 @@
           <t>호출 감사로그</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>서비스 호출 감사로그(§6.3 감사 필수항목)</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
@@ -827,17 +907,22 @@
           <t>접근 업무객체 이력</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>미사용(정의만)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>호출별 접근 업무객체 이력(§6.3 accessed_entity_ids)</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>request_id + entity_type + entity_id</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -857,17 +942,22 @@
           <t>메타데이터 변경이력</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>메타데이터 변경 요약 이력(§7.4)</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -887,17 +977,22 @@
           <t>서비스별 허용 채널/Client 정책</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>미사용(미구현)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>서비스 버전별 허용 채널과 Client 정책(§5.2, §6.2)</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>service_id + version + channel_code</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -917,17 +1012,22 @@
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>미사용(미구현)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>배포된 구현체·JAR/WAR·Bean·Checksum 정보(§8.4 배포·검증)</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -947,17 +1047,22 @@
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>미사용(미구현)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>서비스 등록·변경·활성화 승인 이력(§6.2 운영자 승인, §8.4)</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -977,17 +1082,22 @@
           <t>메타데이터 변경 전/후 이력</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>미사용(미구현)</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>메타데이터 필드 단위 변경 전/후 값 이력(BS_CHANGE_HISTORY는 요약)</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -1007,26 +1117,39 @@
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>미사용(미구현)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>다중 WAS 메타데이터 Cache 무효화 이벤트(§8.4 Registry 갱신)</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>사용 여부 범례: 사용=코드에서 실제 사용 · 미사용(정의만)=엔티티는 있으나 로직 미연결 · 미사용(미구현)=엔티티 없음(설계서 정의만). 기준: 2026-07 master 코드</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1059,162 +1182,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>business_service.bs_change_history</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>메타데이터 변경이력</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>메타데이터 변경 요약 이력(§7.4)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>변경 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>CHG-0001</t>
         </is>
@@ -1231,18 +1354,18 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr"/>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>SERVICE, VERSION, PARAM, ROLE, CLIENT 등</t>
         </is>
@@ -1269,13 +1392,13 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1307,18 +1430,18 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>CREATE, UPDATE, DELETE, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
@@ -1345,13 +1468,13 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1383,13 +1506,13 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>current_timestamp</t>
         </is>
@@ -1421,9 +1544,9 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr"/>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1445,7 +1568,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -1493,246 +1616,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>business_service.bs_service_channel</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>서비스별 허용 채널/Client 정책</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>service_id + version + channel_code</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>서비스 버전별 허용 채널과 Client 정책(§5.2, §6.2)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>channel_code</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, INTERNAL 등</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>허용 채널 코드</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>MCP</t>
         </is>
@@ -1749,18 +1872,18 @@
           <t>char(1)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
@@ -1787,18 +1910,18 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>'ALLOWLIST'</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>ALLOWLIST, DENYLIST, OPEN  ※CHECK</t>
         </is>
@@ -1825,13 +1948,13 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>current_timestamp</t>
         </is>
@@ -1863,13 +1986,13 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1891,7 +2014,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -1939,162 +2062,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>business_service.bs_service_deployment</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>배포된 구현체·JAR/WAR·Bean·Checksum 정보(§8.4 배포·검증)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>배포 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>DEP-0001</t>
         </is>
@@ -2111,13 +2234,13 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr"/>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2149,13 +2272,13 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2187,13 +2310,13 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2225,18 +2348,18 @@
           <t>varchar(10)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>JAR, WAR  ※CHECK</t>
         </is>
@@ -2263,13 +2386,13 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2301,13 +2424,13 @@
           <t>varchar(128)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2339,18 +2462,18 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>'DEPLOYED'</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>DEPLOYED, VERIFIED, FAILED, RETIRED  ※CHECK</t>
         </is>
@@ -2377,18 +2500,18 @@
           <t>char(1)</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr"/>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>'N'</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>Y(검증완료), N(미검증)</t>
         </is>
@@ -2415,13 +2538,13 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr"/>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2453,13 +2576,13 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr"/>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>current_timestamp</t>
         </is>
@@ -2491,9 +2614,9 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr"/>
-      <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2515,7 +2638,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -2563,162 +2686,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>business_service.bs_service_approval</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>서비스 등록·변경·활성화 승인 이력(§6.2 운영자 승인, §8.4)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>승인 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>APR-0001</t>
         </is>
@@ -2735,13 +2858,13 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr"/>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2773,9 +2896,9 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2807,18 +2930,18 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>REGISTER, MODIFY, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
@@ -2845,18 +2968,18 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>'REQUESTED'</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>REQUESTED, APPROVED, REJECTED  ※CHECK</t>
         </is>
@@ -2883,13 +3006,13 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2921,13 +3044,13 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>current_timestamp</t>
         </is>
@@ -2959,9 +3082,9 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr"/>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2993,9 +3116,9 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr"/>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3027,9 +3150,9 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr"/>
-      <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3051,7 +3174,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -3099,162 +3222,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>business_service.bs_service_change_log</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>메타데이터 변경 전/후 이력</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>메타데이터 필드 단위 변경 전/후 값 이력(BS_CHANGE_HISTORY는 요약)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>변경 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>CLG-0001</t>
         </is>
@@ -3271,13 +3394,13 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr"/>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3309,9 +3432,9 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3343,13 +3466,13 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3381,13 +3504,13 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3419,9 +3542,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr"/>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3453,9 +3576,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr"/>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3487,13 +3610,13 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3525,13 +3648,13 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr"/>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>current_timestamp</t>
         </is>
@@ -3553,7 +3676,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -3601,162 +3724,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>business_service.bs_service_cache_event</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>다중 WAS 메타데이터 Cache 무효화 이벤트(§8.4 Registry 갱신)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>캐시 이벤트 ID</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>EVT-0001</t>
         </is>
@@ -3773,9 +3896,9 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr"/>
-      <c r="D8" s="12" t="inlineStr"/>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3807,9 +3930,9 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3841,18 +3964,18 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>INVALIDATE, RELOAD, EVICT_ALL  ※CHECK</t>
         </is>
@@ -3879,13 +4002,13 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>current_timestamp</t>
         </is>
@@ -3917,13 +4040,13 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3955,18 +4078,18 @@
           <t>char(1)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>'N'</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>Y(처리완료), N(미처리)</t>
         </is>
@@ -3993,9 +4116,9 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr"/>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4027,9 +4150,9 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr"/>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4051,7 +4174,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4099,162 +4222,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>business_service.bs_service</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>서비스 Catalog</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Business Service 마스터(서비스 존재 등록). 버전·상태 세부는 BS_SERVICE_VERSION이 담당</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>서비스 고유 식별자(대문자·점 구분, 전역 유일, Handler ID와 일치). 실행/조회 조회키 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
@@ -4271,13 +4394,13 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr"/>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4309,13 +4432,13 @@
           <t>varchar(300)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4347,18 +4470,18 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>CLOSING, JOURNAL, EXPENSE, STATEMENT, CSM (파일럿 5개, 확장 가능)</t>
         </is>
@@ -4385,18 +4508,18 @@
           <t>varchar(10)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>READ(조회), ACTION(실행)  ※CHECK</t>
         </is>
@@ -4423,18 +4546,18 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>'IFRS17'</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>IFRS17 (Phase1 기본·고정, 확장 가능)</t>
         </is>
@@ -4461,13 +4584,13 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4499,18 +4622,18 @@
           <t>char(1)</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
@@ -4537,13 +4660,13 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr"/>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>current_timestamp</t>
         </is>
@@ -4575,13 +4698,13 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr"/>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4613,13 +4736,13 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr"/>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>current_timestamp</t>
         </is>
@@ -4651,13 +4774,13 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr"/>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4679,7 +4802,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4727,204 +4850,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>business_service.bs_service_version</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>service_id + version</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>서비스의 버전별 상태·Schema·Timeout·구현 Bean 정의</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -4941,13 +5064,13 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4979,13 +5102,13 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
@@ -5017,9 +5140,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr"/>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5051,9 +5174,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr"/>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5085,18 +5208,18 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>'ACTIVE'</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>ACTIVE(활성), INACTIVE(비활성)</t>
         </is>
@@ -5123,13 +5246,13 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>current_timestamp</t>
         </is>
@@ -5161,9 +5284,9 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr"/>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5185,7 +5308,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5233,246 +5356,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>business_service.bs_service_param</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>입력 파라미터 정의</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>service_id + version + param_name</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>서비스 버전별 입력 파라미터 명세(§8.3 요청 JSON 명세)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>param_name</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>파라미터 명</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>closingYearMonth</t>
         </is>
@@ -5489,18 +5612,18 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>STRING, NUMBER, BOOLEAN, DATE 등</t>
         </is>
@@ -5527,18 +5650,18 @@
           <t>char(1)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Y(필수), N(선택)</t>
         </is>
@@ -5565,9 +5688,9 @@
           <t>varchar(300)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr"/>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5599,13 +5722,13 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5627,7 +5750,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5675,204 +5798,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>business_service.bs_service_role</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>서비스 역할 권한</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>service_id + role_code</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>서비스 호출에 필요한 허용 역할(§6.2 권한 원칙, §8.3 허용 역할)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>role_code</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>허용 역할 코드(IFRS17 권한체계 기준)</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>IFRS17_CLOSING_VIEW</t>
         </is>
@@ -5889,13 +6012,13 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>current_timestamp</t>
         </is>
@@ -5927,13 +6050,13 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5955,7 +6078,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6003,162 +6126,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>business_service.bs_client</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>호출 Client 등록</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>서비스를 호출하는 Client(채널) 등록(§5.2 X-Client-ID)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>호출 Client 식별자(X-Client-ID) [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
@@ -6175,13 +6298,13 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr"/>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6213,18 +6336,18 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, BATCH 등</t>
         </is>
@@ -6251,9 +6374,9 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr"/>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6285,18 +6408,18 @@
           <t>char(1)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
@@ -6323,13 +6446,13 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>current_timestamp</t>
         </is>
@@ -6361,13 +6484,13 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6389,7 +6512,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6437,204 +6560,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>business_service.bs_client_service</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>Client별 호출 허용</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>client_id + service_id</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Client가 호출 가능한 서비스 매핑(허용 목록)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>Client ID(FK→BS_CLIENT)</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
@@ -6651,18 +6774,18 @@
           <t>char(1)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
@@ -6689,13 +6812,13 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>current_timestamp</t>
         </is>
@@ -6727,13 +6850,13 @@
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6755,7 +6878,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6803,162 +6926,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>business_service.bs_call_log</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>호출 감사로그</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>서비스 호출 감사로그(§6.3 감사 필수항목)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>호출 요청 고유 ID</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>REQ-20260714-0001</t>
         </is>
@@ -6975,9 +7098,9 @@
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr"/>
-      <c r="D8" s="12" t="inlineStr"/>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7009,13 +7132,13 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7047,13 +7170,13 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7085,13 +7208,13 @@
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7123,9 +7246,9 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr"/>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7157,9 +7280,9 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr"/>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7191,13 +7314,13 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7229,9 +7352,9 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr"/>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7263,9 +7386,9 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr"/>
-      <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7297,18 +7420,18 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr"/>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>COMPLETED, PARTIAL, FAILED 등 (부록D)</t>
         </is>
@@ -7335,14 +7458,14 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr"/>
-      <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>200, 400, 401, 403, 404, 500 등</t>
         </is>
@@ -7369,14 +7492,14 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr"/>
-      <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>BS-VAL-001, BS-AUTH-003 등 (부록A)</t>
         </is>
@@ -7403,9 +7526,9 @@
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr"/>
-      <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7437,9 +7560,9 @@
           <t>varchar(128)</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr"/>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7471,9 +7594,9 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr"/>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7505,9 +7628,9 @@
           <t>varchar(64)</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr"/>
-      <c r="D23" s="12" t="inlineStr"/>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7539,9 +7662,9 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr"/>
-      <c r="D24" s="12" t="inlineStr"/>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7563,7 +7686,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -7611,246 +7734,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>business_service.bs_access_entity</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>접근 업무객체 이력</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>request_id + entity_type + entity_id</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
+      <c r="H3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>호출별 접근 업무객체 이력(§6.3 accessed_entity_ids)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
+      <c r="H4" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>호출 요청 ID(FK→BS_CALL_LOG)</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>REQ-20260714-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>entity_type</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>접근 객체 유형</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>CLOSING</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>접근 객체 식별자</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -7867,13 +7990,13 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>current_timestamp</t>
         </is>
@@ -7895,7 +8018,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -75,7 +75,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
@@ -120,7 +120,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -767,9 +767,9 @@
           <t>서비스 역할 권한</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>사용</t>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>미확정</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -802,9 +802,9 @@
           <t>호출 Client 등록</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>사용</t>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>미확정</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -837,9 +837,9 @@
           <t>Client별 호출 허용</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>사용</t>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>미확정</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -872,9 +872,9 @@
           <t>호출 감사로그</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>사용</t>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>미확정</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -907,9 +907,9 @@
           <t>접근 업무객체 이력</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>미사용(정의만)</t>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>미확정</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -942,9 +942,9 @@
           <t>메타데이터 변경이력</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>사용</t>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>미확정</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>미사용(미구현)</t>
+          <t>미확정</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>미사용(미구현)</t>
+          <t>미확정</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>미사용(미구현)</t>
+          <t>미확정</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>미사용(미구현)</t>
+          <t>미확정</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>미사용(미구현)</t>
+          <t>미확정</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>사용 여부 범례: 사용=코드에서 실제 사용 · 미사용(정의만)=엔티티는 있으나 로직 미연결 · 미사용(미구현)=엔티티 없음(설계서 정의만). 기준: 2026-07 master 코드</t>
+          <t>사용 여부 범례: 사용=코드에서 실제 사용 · 미사용(정의만)=엔티티는 있으나 로직 미연결 · 미사용(미구현)=엔티티 없음 · 미확정=공동 검토 전(코드 추정). 현재 확정 3개(BS_SERVICE·BS_SERVICE_VERSION·BS_SERVICE_PARAM), 나머지 11개 미확정</t>
         </is>
       </c>
     </row>

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -764,17 +764,17 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>서비스 역할 권한</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>미확정</t>
+          <t>서비스 필요 권한</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>서비스 호출에 필요한 허용 역할(§6.2 권한 원칙, §8.3 허용 역할)</t>
+          <t>서비스 호출에 필요한 권한(화면ID:액션). 외부 권한API의 사용자 화면권한과 AND 비교(§6.2 권한 원칙)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
+          <t>상세설계서 v1.3 §7.2 (신규) + 권한설계 상세화</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
-          <t>서비스 역할 권한</t>
+          <t>서비스 필요 권한</t>
         </is>
       </c>
       <c r="H2" s="12" t="n"/>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>서비스 호출에 필요한 허용 역할(§6.2 권한 원칙, §8.3 허용 역할)</t>
+          <t>서비스 호출에 필요한 권한(화면ID:액션). 외부 권한API의 사용자 화면권한과 AND 비교(§6.2 권한 원칙)</t>
         </is>
       </c>
       <c r="C4" s="12" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
+          <t>상세설계서 v1.3 §7.2 (신규) + 권한설계 상세화</t>
         </is>
       </c>
       <c r="H4" s="12" t="n"/>
@@ -5985,19 +5985,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>화면ID:액션 형식  ·  화면ID=[A-Z]{4}M[0-9]{3}  ·  액션=inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력)</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>허용 역할 코드(IFRS17 권한체계 기준)</t>
+          <t>필요 권한 코드(화면ID:액션). 외부 권한API의 사용자 화면권한(Y/N)과 AND 비교</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>IFRS17_CLOSING_VIEW</t>
+          <t>CLSGM001:inqy</t>
         </is>
       </c>
     </row>

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -6271,14 +6271,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>형식 {채널}-{시스템}-{일련번호}  ·  정규식 [A-Z0-9]+-[A-Z0-9]+-[0-9]{2}  ·  채널은 하이픈 없는 코드</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>호출 Client 식별자(X-Client-ID) [핵심 로직]</t>
+          <t>호출 Client 식별자(X-Client-ID). 명명규칙 {채널}-{시스템}-{일련번호} [핵심 로직]</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -802,9 +802,9 @@
           <t>호출 Client 등록</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>미확정</t>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -837,9 +837,9 @@
           <t>Client별 호출 허용</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>미확정</t>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -879,7 +879,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>서비스 호출 감사로그(§6.3 감사 필수항목)</t>
+          <t>서비스 호출 감사로그(§6.3). request_id(PK)는 서버 생성 유일값, 호출자 X-Request-ID는 client_request_id에 별도 저장(무결성)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>상세설계서 v1.3 §7.3 (원본)</t>
+          <t>상세설계서 v1.3 §7.3 (원본) + 감사 무결성 보강</t>
         </is>
       </c>
     </row>
@@ -6905,7 +6905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>서비스 호출 감사로그(§6.3 감사 필수항목)</t>
+          <t>서비스 호출 감사로그(§6.3). request_id(PK)는 서버 생성 유일값, 호출자 X-Request-ID는 client_request_id에 별도 저장(무결성)</t>
         </is>
       </c>
       <c r="C4" s="12" t="n"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>상세설계서 v1.3 §7.3 (원본)</t>
+          <t>상세설계서 v1.3 §7.3 (원본) + 감사 무결성 보강</t>
         </is>
       </c>
       <c r="H4" s="12" t="n"/>
@@ -7078,19 +7078,19 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>호출 요청 고유 ID</t>
+          <t>호출 요청 고유 ID — 서버 생성 유일값(호출자 헤더 미사용). 코드 반영 예정 [핵심 로직]</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>REQ-20260714-0001</t>
+          <t>REQ-20260714093012345-1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>trace_id</t>
+          <t>client_request_id</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -7112,32 +7112,28 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>분산추적 ID</t>
+          <t>[신규] 호출자 X-Request-ID 원본(추적·상관용, 유일성 미보장·중복 가능)</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>TRACE-abc123</t>
+          <t>REQ-20260714-0001</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>service_id</t>
+          <t>trace_id</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>varchar(100)</t>
+          <t>varchar(80)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -7150,24 +7146,24 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>호출 서비스 ID</t>
+          <t>분산추적 ID</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>IFRS17.CLOSING.STATUS</t>
+          <t>TRACE-abc123</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>service_version</t>
+          <t>service_id</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>varchar(100)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -7188,24 +7184,24 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>호출 서비스 버전</t>
+          <t>호출 서비스 ID</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>client_id</t>
+          <t>service_version</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>varchar(80)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -7226,28 +7222,32 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>호출 Client ID</t>
+          <t>호출 서비스 버전</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>MCP-IFRS17-01</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>client_id</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>varchar(80)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -7260,19 +7260,19 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>사용자 ID(대리호출 시 실사용자)</t>
+          <t>호출 Client ID</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>E12345</t>
+          <t>MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>department_code</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -7294,32 +7294,28 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>사용자 부서 코드</t>
+          <t>사용자 ID(대리호출 시 실사용자)</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>FIN01</t>
+          <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>requested_at</t>
+          <t>department_code</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D14" s="4" t="inlineStr"/>
       <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -7332,19 +7328,19 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>요청 수신 일시</t>
+          <t>사용자 부서 코드</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14 09:00:00</t>
+          <t>FIN01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>requested_at</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -7353,7 +7349,11 @@
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -7366,24 +7366,24 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>처리 완료 일시</t>
+          <t>요청 수신 일시</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14 09:00:01</t>
+          <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>elapsed_ms</t>
+          <t>completed_at</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -7400,66 +7400,66 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>처리 소요시간(ms)</t>
+          <t>처리 완료 일시</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>2026-07-14 09:00:01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>status_code</t>
+          <t>elapsed_ms</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>COMPLETED, PARTIAL, FAILED 등 (부록D)</t>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>처리 상태</t>
+          <t>처리 소요시간(ms)</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>850</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>http_status</t>
+          <t>status_code</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -7467,29 +7467,29 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>200, 400, 401, 403, 404, 500 등</t>
+          <t>COMPLETED, PARTIAL, FAILED 등 (부록D)</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>HTTP 상태코드</t>
+          <t>처리 상태</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>COMPLETED</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>error_code</t>
+          <t>http_status</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -7501,29 +7501,29 @@
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
-          <t>BS-VAL-001, BS-AUTH-003 등 (부록A)</t>
+          <t>200, 400, 401, 403, 404, 500 등</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>오류코드</t>
+          <t>HTTP 상태코드</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>BS-VAL-001</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>error_id</t>
+          <t>error_code</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>varchar(80)</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -7533,31 +7533,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>BS-VAL-001, BS-AUTH-003 등 (부록A)</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>오류 추적 ID</t>
+          <t>오류코드</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>ERR-xyz789</t>
+          <t>BS-VAL-001</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>parameter_hash</t>
+          <t>error_id</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>varchar(128)</t>
+          <t>varchar(80)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -7574,24 +7574,24 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>요청 파라미터 Hash(원문 저장 금지)</t>
+          <t>오류 추적 ID</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>a1b2c3...</t>
+          <t>ERR-xyz789</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>result_count</t>
+          <t>parameter_hash</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>varchar(128)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -7608,24 +7608,24 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>결과 건수</t>
+          <t>요청 파라미터 Hash(원문 저장 금지)</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>a1b2c3...</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>remote_ip</t>
+          <t>result_count</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>varchar(64)</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -7642,24 +7642,24 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>호출 원격 IP</t>
+          <t>결과 건수</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>10.1.2.3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>server_instance</t>
+          <t>remote_ip</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>varchar(100)</t>
+          <t>varchar(64)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -7676,17 +7676,51 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
+          <t>호출 원격 IP</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>10.1.2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>server_instance</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
           <t>처리 WAS 인스턴스</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>was-01</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -7695,12 +7729,12 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A26:H26"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>분산추적 ID</t>
+          <t>분산추적/장애분석용 선택 pass-through(§5.2 X-Trace-ID, 응답 에코). 운영 주 추적키는 request_id · receiver 그룹핑 로직 없음</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -872,9 +872,9 @@
           <t>호출 감사로그</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>미확정</t>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -907,9 +907,9 @@
           <t>접근 업무객체 이력</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>미확정</t>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>미사용(정의만)</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +70,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="009C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00974706"/>
       <sz val="10"/>
     </font>
     <font>
@@ -170,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -196,16 +202,19 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -944,12 +953,12 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>미확정</t>
+          <t>미사용(범위제외)</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>메타데이터 변경 요약 이력(§7.4)</t>
+          <t>메타데이터 변경 요약 이력(§7.4). ※코드에 recordChange 기록 로직 존재하나 운영 범위 제외(미사용)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -977,7 +986,7 @@
           <t>서비스별 허용 채널/Client 정책</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>미확정</t>
         </is>
@@ -1012,7 +1021,7 @@
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>미확정</t>
         </is>
@@ -1047,7 +1056,7 @@
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>미확정</t>
         </is>
@@ -1082,7 +1091,7 @@
           <t>메타데이터 변경 전/후 이력</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>미확정</t>
         </is>
@@ -1117,7 +1126,7 @@
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>미확정</t>
         </is>
@@ -1139,9 +1148,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>사용 여부 범례: 사용=코드에서 실제 사용 · 미사용(정의만)=엔티티는 있으나 로직 미연결 · 미사용(미구현)=엔티티 없음 · 미확정=공동 검토 전(코드 추정). 현재 확정 3개(BS_SERVICE·BS_SERVICE_VERSION·BS_SERVICE_PARAM), 나머지 11개 미확정</t>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>사용 여부 범례: 사용=코드에서 실제 사용 · 미사용(정의만)=엔티티는 있으나 로직 미연결 · 미사용(미구현)=엔티티 없음 · 미사용(범위제외)=코드에 기록 로직 있으나 운영 범위 제외 · 미확정=공동 검토 전(코드 추정)</t>
         </is>
       </c>
     </row>
@@ -1182,162 +1191,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_change_history</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>메타데이터 변경이력</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>메타데이터 변경 요약 이력(§7.4)</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>메타데이터 변경 요약 이력(§7.4). ※코드에 recordChange 기록 로직 존재하나 운영 범위 제외(미사용)</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>변경 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>CHG-0001</t>
         </is>
@@ -1365,7 +1374,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>SERVICE, VERSION, PARAM, ROLE, CLIENT 등</t>
         </is>
@@ -1441,7 +1450,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>CREATE, UPDATE, DELETE, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
@@ -1568,7 +1577,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -1616,246 +1625,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_channel</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>서비스별 허용 채널/Client 정책</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>service_id + version + channel_code</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스 버전별 허용 채널과 Client 정책(§5.2, §6.2)</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>channel_code</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, INTERNAL 등</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>허용 채널 코드</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>MCP</t>
         </is>
@@ -1883,7 +1892,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
@@ -1921,7 +1930,7 @@
           <t>'ALLOWLIST'</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>ALLOWLIST, DENYLIST, OPEN  ※CHECK</t>
         </is>
@@ -2014,7 +2023,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -2062,162 +2071,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_deployment</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>배포된 구현체·JAR/WAR·Bean·Checksum 정보(§8.4 배포·검증)</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>배포 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>DEP-0001</t>
         </is>
@@ -2359,7 +2368,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>JAR, WAR  ※CHECK</t>
         </is>
@@ -2473,7 +2482,7 @@
           <t>'DEPLOYED'</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>DEPLOYED, VERIFIED, FAILED, RETIRED  ※CHECK</t>
         </is>
@@ -2511,7 +2520,7 @@
           <t>'N'</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>Y(검증완료), N(미검증)</t>
         </is>
@@ -2638,7 +2647,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -2686,162 +2695,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_approval</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스 등록·변경·활성화 승인 이력(§6.2 운영자 승인, §8.4)</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>승인 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>APR-0001</t>
         </is>
@@ -2941,7 +2950,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>REGISTER, MODIFY, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
@@ -2979,7 +2988,7 @@
           <t>'REQUESTED'</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>REQUESTED, APPROVED, REJECTED  ※CHECK</t>
         </is>
@@ -3174,7 +3183,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -3222,162 +3231,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_change_log</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>메타데이터 변경 전/후 이력</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>메타데이터 필드 단위 변경 전/후 값 이력(BS_CHANGE_HISTORY는 요약)</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>변경 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>CLG-0001</t>
         </is>
@@ -3676,7 +3685,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -3724,162 +3733,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_cache_event</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>다중 WAS 메타데이터 Cache 무효화 이벤트(§8.4 Registry 갱신)</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>캐시 이벤트 ID</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>EVT-0001</t>
         </is>
@@ -3975,7 +3984,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>INVALIDATE, RELOAD, EVICT_ALL  ※CHECK</t>
         </is>
@@ -4089,7 +4098,7 @@
           <t>'N'</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>Y(처리완료), N(미처리)</t>
         </is>
@@ -4174,7 +4183,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4222,162 +4231,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>서비스 Catalog</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Business Service 마스터(서비스 존재 등록). 버전·상태 세부는 BS_SERVICE_VERSION이 담당</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>서비스 고유 식별자(대문자·점 구분, 전역 유일, Handler ID와 일치). 실행/조회 조회키 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
@@ -4481,7 +4490,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>CLOSING, JOURNAL, EXPENSE, STATEMENT, CSM (파일럿 5개, 확장 가능)</t>
         </is>
@@ -4519,7 +4528,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>READ(조회), ACTION(실행)  ※CHECK</t>
         </is>
@@ -4557,7 +4566,7 @@
           <t>'IFRS17'</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>IFRS17 (Phase1 기본·고정, 확장 가능)</t>
         </is>
@@ -4633,7 +4642,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
@@ -4802,7 +4811,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4850,204 +4859,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_version</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>service_id + version</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스의 버전별 상태·Schema·Timeout·구현 Bean 정의</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -5219,7 +5228,7 @@
           <t>'ACTIVE'</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>ACTIVE(활성), INACTIVE(비활성)</t>
         </is>
@@ -5308,7 +5317,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5356,246 +5365,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_param</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>입력 파라미터 정의</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>service_id + version + param_name</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스 버전별 입력 파라미터 명세(§8.3 요청 JSON 명세)</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>param_name</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>파라미터 명</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>closingYearMonth</t>
         </is>
@@ -5623,7 +5632,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>STRING, NUMBER, BOOLEAN, DATE 등</t>
         </is>
@@ -5661,7 +5670,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Y(필수), N(선택)</t>
         </is>
@@ -5750,7 +5759,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5798,204 +5807,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_role</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>서비스 필요 권한</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>service_id + role_code</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스 호출에 필요한 권한(화면ID:액션). 외부 권한API의 사용자 화면권한과 AND 비교(§6.2 권한 원칙)</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규) + 권한설계 상세화</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>role_code</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>화면ID:액션 형식  ·  화면ID=[A-Z]{4}M[0-9]{3}  ·  액션=inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력)</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>필요 권한 코드(화면ID:액션). 외부 권한API의 사용자 화면권한(Y/N)과 AND 비교</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>CLSGM001:inqy</t>
         </is>
@@ -6078,7 +6087,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6126,162 +6135,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_client</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>호출 Client 등록</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스를 호출하는 Client(채널) 등록(§5.2 X-Client-ID)</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>형식 {채널}-{시스템}-{일련번호}  ·  정규식 [A-Z0-9]+-[A-Z0-9]+-[0-9]{2}  ·  채널은 하이픈 없는 코드</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>호출 Client 식별자(X-Client-ID). 명명규칙 {채널}-{시스템}-{일련번호} [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
@@ -6347,7 +6356,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, BATCH 등</t>
         </is>
@@ -6419,7 +6428,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
@@ -6512,7 +6521,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6560,204 +6569,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_client_service</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>Client별 호출 허용</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>client_id + service_id</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Client가 호출 가능한 서비스 매핑(허용 목록)</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>Client ID(FK→BS_CLIENT)</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
@@ -6785,7 +6794,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
@@ -6878,7 +6887,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6926,162 +6935,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_call_log</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>호출 감사로그</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스 호출 감사로그(§6.3). request_id(PK)는 서버 생성 유일값, 호출자 X-Request-ID는 client_request_id에 별도 저장(무결성)</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본) + 감사 무결성 보강</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>호출 요청 고유 ID — 서버 생성 유일값(호출자 헤더 미사용). 코드 반영 예정 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>REQ-20260714093012345-1</t>
         </is>
@@ -7465,7 +7474,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>COMPLETED, PARTIAL, FAILED 등 (부록D)</t>
         </is>
@@ -7499,7 +7508,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>200, 400, 401, 403, 404, 500 등</t>
         </is>
@@ -7533,7 +7542,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>BS-VAL-001, BS-AUTH-003 등 (부록A)</t>
         </is>
@@ -7720,7 +7729,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -7768,246 +7777,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_access_entity</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>접근 업무객체 이력</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>request_id + entity_type + entity_id</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>호출별 접근 업무객체 이력(§6.3 accessed_entity_ids)</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>호출 요청 ID(FK→BS_CALL_LOG)</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>REQ-20260714-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>entity_type</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>접근 객체 유형</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>CLOSING</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>접근 객체 식별자</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -8052,7 +8061,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,6 +81,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
@@ -92,7 +98,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -122,6 +128,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -176,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -208,25 +219,28 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -988,7 +1002,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>미확정</t>
+          <t>미사용(미구현)</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1021,7 +1035,7 @@
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>미확정</t>
         </is>
@@ -1056,7 +1070,7 @@
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>미확정</t>
         </is>
@@ -1091,7 +1105,7 @@
           <t>메타데이터 변경 전/후 이력</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>미확정</t>
         </is>
@@ -1126,7 +1140,7 @@
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>미확정</t>
         </is>
@@ -1148,7 +1162,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>사용 여부 범례: 사용=코드에서 실제 사용 · 미사용(정의만)=엔티티는 있으나 로직 미연결 · 미사용(미구현)=엔티티 없음 · 미사용(범위제외)=코드에 기록 로직 있으나 운영 범위 제외 · 미확정=공동 검토 전(코드 추정)</t>
         </is>
@@ -1191,162 +1205,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>business_service.bs_change_history</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>메타데이터 변경이력</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>메타데이터 변경 요약 이력(§7.4). ※코드에 recordChange 기록 로직 존재하나 운영 범위 제외(미사용)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>변경 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>CHG-0001</t>
         </is>
@@ -1374,7 +1388,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>SERVICE, VERSION, PARAM, ROLE, CLIENT 등</t>
         </is>
@@ -1450,7 +1464,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>CREATE, UPDATE, DELETE, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
@@ -1577,7 +1591,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -1625,246 +1639,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>business_service.bs_service_channel</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>서비스별 허용 채널/Client 정책</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>service_id + version + channel_code</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>서비스 버전별 허용 채널과 Client 정책(§5.2, §6.2)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>channel_code</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, INTERNAL 등</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>허용 채널 코드</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>MCP</t>
         </is>
@@ -1892,7 +1906,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
@@ -1930,7 +1944,7 @@
           <t>'ALLOWLIST'</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>ALLOWLIST, DENYLIST, OPEN  ※CHECK</t>
         </is>
@@ -2023,7 +2037,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -2071,162 +2085,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>business_service.bs_service_deployment</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>배포된 구현체·JAR/WAR·Bean·Checksum 정보(§8.4 배포·검증)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>배포 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>DEP-0001</t>
         </is>
@@ -2368,7 +2382,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>JAR, WAR  ※CHECK</t>
         </is>
@@ -2482,7 +2496,7 @@
           <t>'DEPLOYED'</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>DEPLOYED, VERIFIED, FAILED, RETIRED  ※CHECK</t>
         </is>
@@ -2520,7 +2534,7 @@
           <t>'N'</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>Y(검증완료), N(미검증)</t>
         </is>
@@ -2647,7 +2661,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -2695,162 +2709,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>business_service.bs_service_approval</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>서비스 등록·변경·활성화 승인 이력(§6.2 운영자 승인, §8.4)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>승인 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>APR-0001</t>
         </is>
@@ -2950,7 +2964,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>REGISTER, MODIFY, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
@@ -2988,7 +3002,7 @@
           <t>'REQUESTED'</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>REQUESTED, APPROVED, REJECTED  ※CHECK</t>
         </is>
@@ -3183,7 +3197,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -3231,162 +3245,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>business_service.bs_service_change_log</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>메타데이터 변경 전/후 이력</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>메타데이터 필드 단위 변경 전/후 값 이력(BS_CHANGE_HISTORY는 요약)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>변경 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>CLG-0001</t>
         </is>
@@ -3685,7 +3699,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -3733,162 +3747,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>business_service.bs_service_cache_event</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>다중 WAS 메타데이터 Cache 무효화 이벤트(§8.4 Registry 갱신)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>캐시 이벤트 ID</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>EVT-0001</t>
         </is>
@@ -3984,7 +3998,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>INVALIDATE, RELOAD, EVICT_ALL  ※CHECK</t>
         </is>
@@ -4098,7 +4112,7 @@
           <t>'N'</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>Y(처리완료), N(미처리)</t>
         </is>
@@ -4183,7 +4197,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4231,162 +4245,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>business_service.bs_service</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>서비스 Catalog</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Business Service 마스터(서비스 존재 등록). 버전·상태 세부는 BS_SERVICE_VERSION이 담당</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>서비스 고유 식별자(대문자·점 구분, 전역 유일, Handler ID와 일치). 실행/조회 조회키 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
@@ -4490,7 +4504,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>CLOSING, JOURNAL, EXPENSE, STATEMENT, CSM (파일럿 5개, 확장 가능)</t>
         </is>
@@ -4528,7 +4542,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>READ(조회), ACTION(실행)  ※CHECK</t>
         </is>
@@ -4566,7 +4580,7 @@
           <t>'IFRS17'</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>IFRS17 (Phase1 기본·고정, 확장 가능)</t>
         </is>
@@ -4642,7 +4656,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
@@ -4811,7 +4825,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4859,204 +4873,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>business_service.bs_service_version</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>service_id + version</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>서비스의 버전별 상태·Schema·Timeout·구현 Bean 정의</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -5228,7 +5242,7 @@
           <t>'ACTIVE'</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>ACTIVE(활성), INACTIVE(비활성)</t>
         </is>
@@ -5317,7 +5331,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5365,246 +5379,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>business_service.bs_service_param</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>입력 파라미터 정의</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>service_id + version + param_name</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>서비스 버전별 입력 파라미터 명세(§8.3 요청 JSON 명세)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>param_name</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>파라미터 명</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>closingYearMonth</t>
         </is>
@@ -5632,7 +5646,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>STRING, NUMBER, BOOLEAN, DATE 등</t>
         </is>
@@ -5670,7 +5684,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>Y(필수), N(선택)</t>
         </is>
@@ -5759,7 +5773,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5807,204 +5821,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>business_service.bs_service_role</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>서비스 필요 권한</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>service_id + role_code</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>서비스 호출에 필요한 권한(화면ID:액션). 외부 권한API의 사용자 화면권한과 AND 비교(§6.2 권한 원칙)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규) + 권한설계 상세화</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>role_code</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>화면ID:액션 형식  ·  화면ID=[A-Z]{4}M[0-9]{3}  ·  액션=inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력)</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>필요 권한 코드(화면ID:액션). 외부 권한API의 사용자 화면권한(Y/N)과 AND 비교</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>CLSGM001:inqy</t>
         </is>
@@ -6087,7 +6101,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6135,162 +6149,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>business_service.bs_client</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>호출 Client 등록</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>서비스를 호출하는 Client(채널) 등록(§5.2 X-Client-ID)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>형식 {채널}-{시스템}-{일련번호}  ·  정규식 [A-Z0-9]+-[A-Z0-9]+-[0-9]{2}  ·  채널은 하이픈 없는 코드</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>호출 Client 식별자(X-Client-ID). 명명규칙 {채널}-{시스템}-{일련번호} [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
@@ -6356,7 +6370,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, BATCH 등</t>
         </is>
@@ -6428,7 +6442,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
@@ -6521,7 +6535,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6569,204 +6583,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>business_service.bs_client_service</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>Client별 호출 허용</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>client_id + service_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Client가 호출 가능한 서비스 매핑(허용 목록)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>Client ID(FK→BS_CLIENT)</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
@@ -6794,7 +6808,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
@@ -6887,7 +6901,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6935,162 +6949,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>business_service.bs_call_log</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>호출 감사로그</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>서비스 호출 감사로그(§6.3). request_id(PK)는 서버 생성 유일값, 호출자 X-Request-ID는 client_request_id에 별도 저장(무결성)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본) + 감사 무결성 보강</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>호출 요청 고유 ID — 서버 생성 유일값(호출자 헤더 미사용). 코드 반영 예정 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>REQ-20260714093012345-1</t>
         </is>
@@ -7474,7 +7488,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>COMPLETED, PARTIAL, FAILED 등 (부록D)</t>
         </is>
@@ -7508,7 +7522,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>200, 400, 401, 403, 404, 500 등</t>
         </is>
@@ -7542,7 +7556,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>BS-VAL-001, BS-AUTH-003 등 (부록A)</t>
         </is>
@@ -7729,7 +7743,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -7777,246 +7791,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>business_service.bs_access_entity</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>접근 업무객체 이력</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>request_id + entity_type + entity_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>호출별 접근 업무객체 이력(§6.3 accessed_entity_ids)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>호출 요청 ID(FK→BS_CALL_LOG)</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>REQ-20260714-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>entity_type</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>접근 객체 유형</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>CLOSING</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>접근 객체 식별자</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -8061,7 +8075,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -1035,9 +1035,9 @@
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>미확정</t>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>미사용(미구현)</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -1070,9 +1070,9 @@
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>미확정</t>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>미사용(미구현)</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -1105,9 +1105,9 @@
           <t>메타데이터 변경 전/후 이력</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>미확정</t>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>미사용(미구현)</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,18 +87,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="009C0006"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -133,11 +127,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -187,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -219,28 +208,25 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1140,9 +1126,9 @@
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>미확정</t>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>미사용(미구현)</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1162,7 +1148,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>사용 여부 범례: 사용=코드에서 실제 사용 · 미사용(정의만)=엔티티는 있으나 로직 미연결 · 미사용(미구현)=엔티티 없음 · 미사용(범위제외)=코드에 기록 로직 있으나 운영 범위 제외 · 미확정=공동 검토 전(코드 추정)</t>
         </is>
@@ -1205,162 +1191,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_change_history</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>메타데이터 변경이력</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>메타데이터 변경 요약 이력(§7.4). ※코드에 recordChange 기록 로직 존재하나 운영 범위 제외(미사용)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>변경 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>CHG-0001</t>
         </is>
@@ -1388,7 +1374,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>SERVICE, VERSION, PARAM, ROLE, CLIENT 등</t>
         </is>
@@ -1464,7 +1450,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>CREATE, UPDATE, DELETE, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
@@ -1591,7 +1577,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -1639,246 +1625,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_channel</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>서비스별 허용 채널/Client 정책</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>service_id + version + channel_code</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스 버전별 허용 채널과 Client 정책(§5.2, §6.2)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>channel_code</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, INTERNAL 등</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>허용 채널 코드</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>MCP</t>
         </is>
@@ -1906,7 +1892,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
@@ -1944,7 +1930,7 @@
           <t>'ALLOWLIST'</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>ALLOWLIST, DENYLIST, OPEN  ※CHECK</t>
         </is>
@@ -2037,7 +2023,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -2085,162 +2071,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_deployment</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>배포된 구현체·JAR/WAR·Bean·Checksum 정보(§8.4 배포·검증)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>배포 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>DEP-0001</t>
         </is>
@@ -2382,7 +2368,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>JAR, WAR  ※CHECK</t>
         </is>
@@ -2496,7 +2482,7 @@
           <t>'DEPLOYED'</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>DEPLOYED, VERIFIED, FAILED, RETIRED  ※CHECK</t>
         </is>
@@ -2534,7 +2520,7 @@
           <t>'N'</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>Y(검증완료), N(미검증)</t>
         </is>
@@ -2661,7 +2647,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -2709,162 +2695,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_approval</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스 등록·변경·활성화 승인 이력(§6.2 운영자 승인, §8.4)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>승인 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>APR-0001</t>
         </is>
@@ -2964,7 +2950,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>REGISTER, MODIFY, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
@@ -3002,7 +2988,7 @@
           <t>'REQUESTED'</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>REQUESTED, APPROVED, REJECTED  ※CHECK</t>
         </is>
@@ -3197,7 +3183,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -3245,162 +3231,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_change_log</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>메타데이터 변경 전/후 이력</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>메타데이터 필드 단위 변경 전/후 값 이력(BS_CHANGE_HISTORY는 요약)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>변경 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>CLG-0001</t>
         </is>
@@ -3699,7 +3685,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -3747,162 +3733,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_cache_event</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>다중 WAS 메타데이터 Cache 무효화 이벤트(§8.4 Registry 갱신)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>캐시 이벤트 ID</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>EVT-0001</t>
         </is>
@@ -3998,7 +3984,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>INVALIDATE, RELOAD, EVICT_ALL  ※CHECK</t>
         </is>
@@ -4112,7 +4098,7 @@
           <t>'N'</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>Y(처리완료), N(미처리)</t>
         </is>
@@ -4197,7 +4183,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4245,162 +4231,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>서비스 Catalog</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Business Service 마스터(서비스 존재 등록). 버전·상태 세부는 BS_SERVICE_VERSION이 담당</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>서비스 고유 식별자(대문자·점 구분, 전역 유일, Handler ID와 일치). 실행/조회 조회키 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
@@ -4504,7 +4490,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>CLOSING, JOURNAL, EXPENSE, STATEMENT, CSM (파일럿 5개, 확장 가능)</t>
         </is>
@@ -4542,7 +4528,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>READ(조회), ACTION(실행)  ※CHECK</t>
         </is>
@@ -4580,7 +4566,7 @@
           <t>'IFRS17'</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>IFRS17 (Phase1 기본·고정, 확장 가능)</t>
         </is>
@@ -4656,7 +4642,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
@@ -4825,7 +4811,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4873,204 +4859,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_version</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>service_id + version</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스의 버전별 상태·Schema·Timeout·구현 Bean 정의</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -5242,7 +5228,7 @@
           <t>'ACTIVE'</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>ACTIVE(활성), INACTIVE(비활성)</t>
         </is>
@@ -5331,7 +5317,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5379,246 +5365,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_param</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>입력 파라미터 정의</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>service_id + version + param_name</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스 버전별 입력 파라미터 명세(§8.3 요청 JSON 명세)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>param_name</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>파라미터 명</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>closingYearMonth</t>
         </is>
@@ -5646,7 +5632,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>STRING, NUMBER, BOOLEAN, DATE 등</t>
         </is>
@@ -5684,7 +5670,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Y(필수), N(선택)</t>
         </is>
@@ -5773,7 +5759,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5821,204 +5807,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_role</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>서비스 필요 권한</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>service_id + role_code</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스 호출에 필요한 권한(화면ID:액션). 외부 권한API의 사용자 화면권한과 AND 비교(§6.2 권한 원칙)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규) + 권한설계 상세화</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>role_code</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>화면ID:액션 형식  ·  화면ID=[A-Z]{4}M[0-9]{3}  ·  액션=inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>필요 권한 코드(화면ID:액션). 외부 권한API의 사용자 화면권한(Y/N)과 AND 비교</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>CLSGM001:inqy</t>
         </is>
@@ -6101,7 +6087,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6149,162 +6135,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_client</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>호출 Client 등록</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스를 호출하는 Client(채널) 등록(§5.2 X-Client-ID)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>형식 {채널}-{시스템}-{일련번호}  ·  정규식 [A-Z0-9]+-[A-Z0-9]+-[0-9]{2}  ·  채널은 하이픈 없는 코드</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>호출 Client 식별자(X-Client-ID). 명명규칙 {채널}-{시스템}-{일련번호} [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
@@ -6370,7 +6356,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, BATCH 등</t>
         </is>
@@ -6442,7 +6428,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
@@ -6535,7 +6521,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6583,204 +6569,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_client_service</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>Client별 호출 허용</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>client_id + service_id</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Client가 호출 가능한 서비스 매핑(허용 목록)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>Client ID(FK→BS_CLIENT)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
@@ -6808,7 +6794,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
@@ -6901,7 +6887,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6949,162 +6935,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_call_log</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>호출 감사로그</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스 호출 감사로그(§6.3). request_id(PK)는 서버 생성 유일값, 호출자 X-Request-ID는 client_request_id에 별도 저장(무결성)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본) + 감사 무결성 보강</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>호출 요청 고유 ID — 서버 생성 유일값(호출자 헤더 미사용). 코드 반영 예정 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>REQ-20260714093012345-1</t>
         </is>
@@ -7488,7 +7474,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>COMPLETED, PARTIAL, FAILED 등 (부록D)</t>
         </is>
@@ -7522,7 +7508,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>200, 400, 401, 403, 404, 500 등</t>
         </is>
@@ -7556,7 +7542,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>BS-VAL-001, BS-AUTH-003 등 (부록A)</t>
         </is>
@@ -7743,7 +7729,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -7791,246 +7777,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_access_entity</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>접근 업무객체 이력</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>request_id + entity_type + entity_id</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>호출별 접근 업무객체 이력(§6.3 accessed_entity_ids)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>호출 요청 ID(FK→BS_CALL_LOG)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>REQ-20260714-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>entity_type</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>접근 객체 유형</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>CLOSING</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>접근 객체 식별자</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -8075,7 +8061,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,19 +69,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="009C6500"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00974706"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
@@ -92,7 +80,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -121,12 +109,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -176,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -202,31 +185,25 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -743,7 +720,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>미사용(정의만)</t>
+          <t>미사용</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -918,7 +895,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>미사용(정의만)</t>
+          <t>미사용</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -951,9 +928,9 @@
           <t>메타데이터 변경이력</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>미사용(범위제외)</t>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>미사용</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -986,9 +963,9 @@
           <t>서비스별 허용 채널/Client 정책</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>미사용(미구현)</t>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>미사용</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1021,9 +998,9 @@
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>미사용(미구현)</t>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>미사용</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1056,9 +1033,9 @@
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>미사용(미구현)</t>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>미사용</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1091,9 +1068,9 @@
           <t>메타데이터 변경 전/후 이력</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>미사용(미구현)</t>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>미사용</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1126,9 +1103,9 @@
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>미사용(미구현)</t>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>미사용</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1148,9 +1125,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>사용 여부 범례: 사용=코드에서 실제 사용 · 미사용(정의만)=엔티티는 있으나 로직 미연결 · 미사용(미구현)=엔티티 없음 · 미사용(범위제외)=코드에 기록 로직 있으나 운영 범위 제외 · 미확정=공동 검토 전(코드 추정)</t>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>사용 여부 범례: 사용=Phase1 코드에서 실제 사용(6개) · 미사용=Phase1 미사용(8개, 정의만/범위제외/미구현 등 향후 확장·예약 포함)</t>
         </is>
       </c>
     </row>
@@ -1191,162 +1168,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_change_history</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>메타데이터 변경이력</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>메타데이터 변경 요약 이력(§7.4). ※코드에 recordChange 기록 로직 존재하나 운영 범위 제외(미사용)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>변경 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>CHG-0001</t>
         </is>
@@ -1374,7 +1351,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>SERVICE, VERSION, PARAM, ROLE, CLIENT 등</t>
         </is>
@@ -1450,7 +1427,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>CREATE, UPDATE, DELETE, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
@@ -1577,7 +1554,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -1625,246 +1602,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_channel</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>서비스별 허용 채널/Client 정책</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>service_id + version + channel_code</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>서비스 버전별 허용 채널과 Client 정책(§5.2, §6.2)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>channel_code</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, INTERNAL 등</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>허용 채널 코드</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>MCP</t>
         </is>
@@ -1892,7 +1869,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
@@ -1930,7 +1907,7 @@
           <t>'ALLOWLIST'</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>ALLOWLIST, DENYLIST, OPEN  ※CHECK</t>
         </is>
@@ -2023,7 +2000,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -2071,162 +2048,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_deployment</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>배포된 구현체·JAR/WAR·Bean·Checksum 정보(§8.4 배포·검증)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>배포 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>DEP-0001</t>
         </is>
@@ -2368,7 +2345,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>JAR, WAR  ※CHECK</t>
         </is>
@@ -2482,7 +2459,7 @@
           <t>'DEPLOYED'</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>DEPLOYED, VERIFIED, FAILED, RETIRED  ※CHECK</t>
         </is>
@@ -2520,7 +2497,7 @@
           <t>'N'</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>Y(검증완료), N(미검증)</t>
         </is>
@@ -2647,7 +2624,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -2695,162 +2672,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_approval</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>서비스 등록·변경·활성화 승인 이력(§6.2 운영자 승인, §8.4)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>승인 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>APR-0001</t>
         </is>
@@ -2950,7 +2927,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>REGISTER, MODIFY, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
@@ -2988,7 +2965,7 @@
           <t>'REQUESTED'</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>REQUESTED, APPROVED, REJECTED  ※CHECK</t>
         </is>
@@ -3183,7 +3160,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -3231,162 +3208,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_change_log</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>메타데이터 변경 전/후 이력</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>메타데이터 필드 단위 변경 전/후 값 이력(BS_CHANGE_HISTORY는 요약)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>변경 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>CLG-0001</t>
         </is>
@@ -3685,7 +3662,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -3733,162 +3710,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_cache_event</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>다중 WAS 메타데이터 Cache 무효화 이벤트(§8.4 Registry 갱신)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>캐시 이벤트 ID</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>EVT-0001</t>
         </is>
@@ -3984,7 +3961,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>INVALIDATE, RELOAD, EVICT_ALL  ※CHECK</t>
         </is>
@@ -4098,7 +4075,7 @@
           <t>'N'</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>Y(처리완료), N(미처리)</t>
         </is>
@@ -4183,7 +4160,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4231,162 +4208,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>서비스 Catalog</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Business Service 마스터(서비스 존재 등록). 버전·상태 세부는 BS_SERVICE_VERSION이 담당</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>서비스 고유 식별자(대문자·점 구분, 전역 유일, Handler ID와 일치). 실행/조회 조회키 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
@@ -4490,7 +4467,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>CLOSING, JOURNAL, EXPENSE, STATEMENT, CSM (파일럿 5개, 확장 가능)</t>
         </is>
@@ -4528,7 +4505,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>READ(조회), ACTION(실행)  ※CHECK</t>
         </is>
@@ -4566,7 +4543,7 @@
           <t>'IFRS17'</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>IFRS17 (Phase1 기본·고정, 확장 가능)</t>
         </is>
@@ -4642,7 +4619,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
@@ -4811,7 +4788,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4859,204 +4836,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_version</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>service_id + version</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>서비스의 버전별 상태·Schema·Timeout·구현 Bean 정의</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -5228,7 +5205,7 @@
           <t>'ACTIVE'</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>ACTIVE(활성), INACTIVE(비활성)</t>
         </is>
@@ -5317,7 +5294,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5365,246 +5342,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_param</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>입력 파라미터 정의</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>service_id + version + param_name</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>서비스 버전별 입력 파라미터 명세(§8.3 요청 JSON 명세)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>param_name</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>파라미터 명</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>closingYearMonth</t>
         </is>
@@ -5632,7 +5609,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>STRING, NUMBER, BOOLEAN, DATE 등</t>
         </is>
@@ -5670,7 +5647,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>Y(필수), N(선택)</t>
         </is>
@@ -5759,7 +5736,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5807,204 +5784,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_role</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>서비스 필요 권한</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>service_id + role_code</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>서비스 호출에 필요한 권한(화면ID:액션). 외부 권한API의 사용자 화면권한과 AND 비교(§6.2 권한 원칙)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규) + 권한설계 상세화</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>role_code</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>화면ID:액션 형식  ·  화면ID=[A-Z]{4}M[0-9]{3}  ·  액션=inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력)</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>필요 권한 코드(화면ID:액션). 외부 권한API의 사용자 화면권한(Y/N)과 AND 비교</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>CLSGM001:inqy</t>
         </is>
@@ -6087,7 +6064,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6135,162 +6112,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_client</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>호출 Client 등록</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>서비스를 호출하는 Client(채널) 등록(§5.2 X-Client-ID)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>형식 {채널}-{시스템}-{일련번호}  ·  정규식 [A-Z0-9]+-[A-Z0-9]+-[0-9]{2}  ·  채널은 하이픈 없는 코드</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>호출 Client 식별자(X-Client-ID). 명명규칙 {채널}-{시스템}-{일련번호} [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
@@ -6356,7 +6333,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, BATCH 등</t>
         </is>
@@ -6428,7 +6405,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
@@ -6521,7 +6498,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6569,204 +6546,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_client_service</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>Client별 호출 허용</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>client_id + service_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Client가 호출 가능한 서비스 매핑(허용 목록)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>Client ID(FK→BS_CLIENT)</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
@@ -6794,7 +6771,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
@@ -6887,7 +6864,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6935,162 +6912,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_call_log</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>호출 감사로그</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>서비스 호출 감사로그(§6.3). request_id(PK)는 서버 생성 유일값, 호출자 X-Request-ID는 client_request_id에 별도 저장(무결성)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본) + 감사 무결성 보강</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>호출 요청 고유 ID — 서버 생성 유일값(호출자 헤더 미사용). 코드 반영 예정 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>REQ-20260714093012345-1</t>
         </is>
@@ -7474,7 +7451,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>COMPLETED, PARTIAL, FAILED 등 (부록D)</t>
         </is>
@@ -7508,7 +7485,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>200, 400, 401, 403, 404, 500 등</t>
         </is>
@@ -7542,7 +7519,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>BS-VAL-001, BS-AUTH-003 등 (부록A)</t>
         </is>
@@ -7729,7 +7706,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -7777,246 +7754,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_access_entity</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>접근 업무객체 이력</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>request_id + entity_type + entity_id</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>호출별 접근 업무객체 이력(§6.3 accessed_entity_ids)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="11" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>호출 요청 ID(FK→BS_CALL_LOG)</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>REQ-20260714-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>entity_type</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>접근 객체 유형</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>CLOSING</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>접근 객체 식별자</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -8061,7 +8038,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -80,7 +80,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -99,37 +99,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -159,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -176,35 +151,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -663,7 +626,7 @@
           <t>service_id</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
@@ -698,7 +661,7 @@
           <t>service_id + version</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
@@ -718,7 +681,7 @@
           <t>입력 파라미터 정의</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
@@ -873,7 +836,7 @@
           <t>request_id</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본) + 감사 무결성 보강</t>
         </is>
@@ -893,7 +856,7 @@
           <t>접근 업무객체 이력</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
@@ -928,7 +891,7 @@
           <t>메타데이터 변경이력</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
@@ -963,7 +926,7 @@
           <t>서비스별 허용 채널/Client 정책</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
@@ -998,7 +961,7 @@
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
@@ -1033,7 +996,7 @@
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
@@ -1068,7 +1031,7 @@
           <t>메타데이터 변경 전/후 이력</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
@@ -1103,7 +1066,7 @@
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
@@ -1125,7 +1088,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>사용 여부 범례: 사용=Phase1 코드에서 실제 사용(6개) · 미사용=Phase1 미사용(8개, 정의만/범위제외/미구현 등 향후 확장·예약 포함)</t>
         </is>
@@ -1168,162 +1131,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>business_service.bs_change_history</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>메타데이터 변경이력</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>메타데이터 변경 요약 이력(§7.4). ※코드에 recordChange 기록 로직 존재하나 운영 범위 제외(미사용)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>변경 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>CHG-0001</t>
         </is>
@@ -1351,7 +1314,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>SERVICE, VERSION, PARAM, ROLE, CLIENT 등</t>
         </is>
@@ -1427,7 +1390,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>CREATE, UPDATE, DELETE, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
@@ -1554,9 +1517,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>
@@ -1602,246 +1565,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>business_service.bs_service_channel</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>서비스별 허용 채널/Client 정책</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>service_id + version + channel_code</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>서비스 버전별 허용 채널과 Client 정책(§5.2, §6.2)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>channel_code</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, INTERNAL 등</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>허용 채널 코드</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>MCP</t>
         </is>
@@ -1869,7 +1832,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
@@ -1907,7 +1870,7 @@
           <t>'ALLOWLIST'</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>ALLOWLIST, DENYLIST, OPEN  ※CHECK</t>
         </is>
@@ -2000,9 +1963,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>
@@ -2048,162 +2011,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>business_service.bs_service_deployment</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>배포된 구현체·JAR/WAR·Bean·Checksum 정보(§8.4 배포·검증)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>배포 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>DEP-0001</t>
         </is>
@@ -2345,7 +2308,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>JAR, WAR  ※CHECK</t>
         </is>
@@ -2459,7 +2422,7 @@
           <t>'DEPLOYED'</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>DEPLOYED, VERIFIED, FAILED, RETIRED  ※CHECK</t>
         </is>
@@ -2497,7 +2460,7 @@
           <t>'N'</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Y(검증완료), N(미검증)</t>
         </is>
@@ -2624,9 +2587,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>
@@ -2672,162 +2635,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>business_service.bs_service_approval</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>서비스 등록·변경·활성화 승인 이력(§6.2 운영자 승인, §8.4)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>승인 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>APR-0001</t>
         </is>
@@ -2927,7 +2890,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>REGISTER, MODIFY, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
@@ -2965,7 +2928,7 @@
           <t>'REQUESTED'</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>REQUESTED, APPROVED, REJECTED  ※CHECK</t>
         </is>
@@ -3160,9 +3123,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>
@@ -3208,162 +3171,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>business_service.bs_service_change_log</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>메타데이터 변경 전/후 이력</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>메타데이터 필드 단위 변경 전/후 값 이력(BS_CHANGE_HISTORY는 요약)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>변경 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>CLG-0001</t>
         </is>
@@ -3662,9 +3625,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>
@@ -3710,162 +3673,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>business_service.bs_service_cache_event</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>다중 WAS 메타데이터 Cache 무효화 이벤트(§8.4 Registry 갱신)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>캐시 이벤트 ID</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>EVT-0001</t>
         </is>
@@ -3961,7 +3924,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>INVALIDATE, RELOAD, EVICT_ALL  ※CHECK</t>
         </is>
@@ -4075,7 +4038,7 @@
           <t>'N'</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Y(처리완료), N(미처리)</t>
         </is>
@@ -4160,9 +4123,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>
@@ -4208,162 +4171,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>business_service.bs_service</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>서비스 Catalog</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Business Service 마스터(서비스 존재 등록). 버전·상태 세부는 BS_SERVICE_VERSION이 담당</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>서비스 고유 식별자(대문자·점 구분, 전역 유일, Handler ID와 일치). 실행/조회 조회키 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
@@ -4467,7 +4430,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>CLOSING, JOURNAL, EXPENSE, STATEMENT, CSM (파일럿 5개, 확장 가능)</t>
         </is>
@@ -4505,7 +4468,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>READ(조회), ACTION(실행)  ※CHECK</t>
         </is>
@@ -4543,7 +4506,7 @@
           <t>'IFRS17'</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>IFRS17 (Phase1 기본·고정, 확장 가능)</t>
         </is>
@@ -4619,7 +4582,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
@@ -4788,9 +4751,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>
@@ -4836,204 +4799,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>business_service.bs_service_version</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>service_id + version</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>서비스의 버전별 상태·Schema·Timeout·구현 Bean 정의</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -5205,7 +5168,7 @@
           <t>'ACTIVE'</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>ACTIVE(활성), INACTIVE(비활성)</t>
         </is>
@@ -5294,9 +5257,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>
@@ -5342,246 +5305,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>business_service.bs_service_param</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>입력 파라미터 정의</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>service_id + version + param_name</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>서비스 버전별 입력 파라미터 명세(§8.3 요청 JSON 명세)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>param_name</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>파라미터 명</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>closingYearMonth</t>
         </is>
@@ -5609,7 +5572,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>STRING, NUMBER, BOOLEAN, DATE 등</t>
         </is>
@@ -5647,7 +5610,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Y(필수), N(선택)</t>
         </is>
@@ -5736,9 +5699,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>
@@ -5784,204 +5747,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>business_service.bs_service_role</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>서비스 필요 권한</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>service_id + role_code</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>서비스 호출에 필요한 권한(화면ID:액션). 외부 권한API의 사용자 화면권한과 AND 비교(§6.2 권한 원칙)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규) + 권한설계 상세화</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>role_code</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>화면ID:액션 형식  ·  화면ID=[A-Z]{4}M[0-9]{3}  ·  액션=inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력)</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>필요 권한 코드(화면ID:액션). 외부 권한API의 사용자 화면권한(Y/N)과 AND 비교</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>CLSGM001:inqy</t>
         </is>
@@ -6064,9 +6027,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>
@@ -6112,162 +6075,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>business_service.bs_client</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>호출 Client 등록</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>서비스를 호출하는 Client(채널) 등록(§5.2 X-Client-ID)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>형식 {채널}-{시스템}-{일련번호}  ·  정규식 [A-Z0-9]+-[A-Z0-9]+-[0-9]{2}  ·  채널은 하이픈 없는 코드</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>호출 Client 식별자(X-Client-ID). 명명규칙 {채널}-{시스템}-{일련번호} [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
@@ -6333,7 +6296,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, BATCH 등</t>
         </is>
@@ -6405,7 +6368,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
@@ -6498,9 +6461,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>
@@ -6546,204 +6509,204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>business_service.bs_client_service</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>Client별 호출 허용</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>client_id + service_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Client가 호출 가능한 서비스 매핑(허용 목록)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Client ID(FK→BS_CLIENT)</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
@@ -6771,7 +6734,7 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
@@ -6864,9 +6827,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>
@@ -6912,162 +6875,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>business_service.bs_call_log</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>호출 감사로그</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>서비스 호출 감사로그(§6.3). request_id(PK)는 서버 생성 유일값, 호출자 X-Request-ID는 client_request_id에 별도 저장(무결성)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본) + 감사 무결성 보강</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>호출 요청 고유 ID — 서버 생성 유일값(호출자 헤더 미사용). 코드 반영 예정 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>REQ-20260714093012345-1</t>
         </is>
@@ -7451,7 +7414,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>COMPLETED, PARTIAL, FAILED 등 (부록D)</t>
         </is>
@@ -7485,7 +7448,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>200, 400, 401, 403, 404, 500 등</t>
         </is>
@@ -7519,7 +7482,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>BS-VAL-001, BS-AUTH-003 등 (부록A)</t>
         </is>
@@ -7706,9 +7669,9 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>
@@ -7754,246 +7717,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>business_service.bs_access_entity</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>접근 업무객체 이력</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>request_id + entity_type + entity_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>호출별 접근 업무객체 이력(§6.3 accessed_entity_ids)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>호출 요청 ID(FK→BS_CALL_LOG)</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>REQ-20260714-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>entity_type</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>접근 객체 유형</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>CLOSING</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>접근 객체 식별자</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -8038,9 +8001,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재(연녹 음영) · PK 컬럼 음영 · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,6 +65,13 @@
       <b val="1"/>
       <color rgb="00006100"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -134,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -148,23 +155,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -606,27 +619,27 @@
           <t>BS_SERVICE</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>서비스 Catalog</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Business Service 마스터(서비스 존재 등록). 버전·상태 세부는 BS_SERVICE_VERSION이 담당</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
@@ -641,27 +654,27 @@
           <t>BS_SERVICE_VERSION</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>서비스의 버전별 상태·Schema·Timeout·구현 Bean 정의</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>service_id + version</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
@@ -676,27 +689,27 @@
           <t>BS_SERVICE_PARAM</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>입력 파라미터 정의</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>서비스 버전별 입력 파라미터 명세(§8.3 요청 JSON 명세)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>service_id + version + param_name</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -711,27 +724,27 @@
           <t>BS_SERVICE_ROLE</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>서비스 필요 권한</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>서비스 호출에 필요한 권한(화면ID:액션). 외부 권한API의 사용자 화면권한과 AND 비교(§6.2 권한 원칙)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>service_id + role_code</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규) + 권한설계 상세화</t>
         </is>
@@ -746,27 +759,27 @@
           <t>BS_CLIENT</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>호출 Client 등록</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>서비스를 호출하는 Client(채널) 등록(§5.2 X-Client-ID)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -781,27 +794,27 @@
           <t>BS_CLIENT_SERVICE</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Client별 호출 허용</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Client가 호출 가능한 서비스 매핑(허용 목록)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>client_id + service_id</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -816,27 +829,27 @@
           <t>BS_CALL_LOG</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>호출 감사로그</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>서비스 호출 감사로그(§6.3). request_id(PK)는 서버 생성 유일값, 호출자 X-Request-ID는 client_request_id에 별도 저장(무결성)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본) + 감사 무결성 보강</t>
         </is>
@@ -851,27 +864,27 @@
           <t>BS_ACCESS_ENTITY</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>접근 업무객체 이력</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>호출별 접근 업무객체 이력(§6.3 accessed_entity_ids)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>request_id + entity_type + entity_id</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -886,27 +899,27 @@
           <t>BS_CHANGE_HISTORY</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>메타데이터 변경이력</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>메타데이터 변경 요약 이력(§7.4). ※코드에 recordChange 기록 로직 존재하나 운영 범위 제외(미사용)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -921,27 +934,27 @@
           <t>BS_SERVICE_CHANNEL</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>서비스별 허용 채널/Client 정책</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>서비스 버전별 허용 채널과 Client 정책(§5.2, §6.2)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>service_id + version + channel_code</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -956,27 +969,27 @@
           <t>BS_SERVICE_DEPLOYMENT</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>배포된 구현체·JAR/WAR·Bean·Checksum 정보(§8.4 배포·검증)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -991,27 +1004,27 @@
           <t>BS_SERVICE_APPROVAL</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>서비스 등록·변경·활성화 승인 이력(§6.2 운영자 승인, §8.4)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -1026,27 +1039,27 @@
           <t>BS_SERVICE_CHANGE_LOG</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>메타데이터 변경 전/후 이력</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>메타데이터 필드 단위 변경 전/후 값 이력(BS_CHANGE_HISTORY는 요약)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
@@ -1061,34 +1074,34 @@
           <t>BS_SERVICE_CACHE_EVENT</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>다중 WAS 메타데이터 Cache 무효화 이벤트(§8.4 Registry 갱신)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>사용 여부 범례: 사용=Phase1 코드에서 실제 사용(6개) · 미사용=Phase1 미사용(8개, 정의만/범위제외/미구현 등 향후 확장·예약 포함)</t>
         </is>
@@ -1100,6 +1113,22 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1131,132 +1160,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_change_history</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>메타데이터 변경이력</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>메타데이터 변경 요약 이력(§7.4). ※코드에 recordChange 기록 로직 존재하나 운영 범위 제외(미사용)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -1276,29 +1312,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>변경 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>CHG-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>entity_type</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
@@ -1314,29 +1350,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>SERVICE, VERSION, PARAM, ROLE, CLIENT 등</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>변경 대상 유형</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>SERVICE</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
@@ -1352,29 +1388,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>변경 대상 식별자</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>change_type</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -1390,29 +1426,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>CREATE, UPDATE, DELETE, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>변경 유형</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>UPDATE</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>changed_by</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -1428,29 +1464,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>변경자 ID</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>changed_at</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -1466,29 +1502,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>변경 일시</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>2026-07-30 10:00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>change_summary</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>varchar(500)</t>
         </is>
@@ -1500,24 +1536,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>변경 요약</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>timeout_ms 30000→60000</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -1534,6 +1570,9 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1565,132 +1604,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_channel</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>서비스별 허용 채널/Client 정책</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>service_id + version + channel_code</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>서비스 버전별 허용 채널과 Client 정책(§5.2, §6.2)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -1710,29 +1756,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -1752,29 +1798,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>channel_code</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -1794,29 +1840,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, INTERNAL 등</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>허용 채널 코드</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>MCP</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>allow_yn</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>char(1)</t>
         </is>
@@ -1832,29 +1878,29 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>채널 허용 여부</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>client_policy</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -1870,29 +1916,29 @@
           <t>'ALLOWLIST'</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>ALLOWLIST, DENYLIST, OPEN  ※CHECK</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Client 접근 정책</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>ALLOWLIST</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -1908,29 +1954,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>등록 일시</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>created_by</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -1946,24 +1992,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>등록자 ID</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -1980,6 +2026,9 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2011,132 +2060,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_deployment</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>배포된 구현체·JAR/WAR·Bean·Checksum 정보(§8.4 배포·검증)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -2156,29 +2212,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>배포 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>DEP-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -2194,29 +2250,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -2232,29 +2288,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>implementation_bean</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
@@ -2270,29 +2326,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>배포된 Spring Bean 명</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>closingStatusBusinessService</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>artifact_type</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>varchar(10)</t>
         </is>
@@ -2308,29 +2364,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>JAR, WAR  ※CHECK</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>배포 산출물 유형</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>JAR</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>artifact_name</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
@@ -2346,29 +2402,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>배포 산출물 파일명</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>bsl-closing-1.0.jar</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>checksum</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>varchar(128)</t>
         </is>
@@ -2384,29 +2440,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>산출물 무결성 체크섬(SHA-256 등)</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>9f86d0...</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>deploy_status</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -2422,29 +2478,29 @@
           <t>'DEPLOYED'</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>DEPLOYED, VERIFIED, FAILED, RETIRED  ※CHECK</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>배포 상태</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>DEPLOYED</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>bean_verified_yn</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>char(1)</t>
         </is>
@@ -2460,29 +2516,29 @@
           <t>'N'</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Y(검증완료), N(미검증)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Bean 존재·Interface 검증 여부(§8.4)</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>deployed_by</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -2498,29 +2554,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>배포자 ID</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>deployed_at</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -2536,29 +2592,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>배포 일시</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>2026-07-14 08:00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>server_instance</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -2570,24 +2626,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>배포 대상 WAS 인스턴스</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>was-01</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -2604,6 +2660,9 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2635,132 +2694,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_approval</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>서비스 등록·변경·활성화 승인 이력(§6.2 운영자 승인, §8.4)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -2780,29 +2846,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>승인 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>APR-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -2818,29 +2884,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -2852,29 +2918,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>request_type</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -2890,29 +2956,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>REGISTER, MODIFY, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>승인 요청 유형</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>REGISTER</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>approval_status</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -2928,29 +2994,29 @@
           <t>'REQUESTED'</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>REQUESTED, APPROVED, REJECTED  ※CHECK</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>승인 상태</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>requested_by</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -2966,29 +3032,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>요청자 ID</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>requested_at</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -3004,29 +3070,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>요청 일시</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>2026-07-14 08:30:00</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -3038,29 +3104,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>승인자 ID</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>E67890</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>approved_at</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -3072,29 +3138,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>승인 일시</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>approval_comment</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>varchar(500)</t>
         </is>
@@ -3106,24 +3172,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>승인/반려 사유</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>최초 등록 승인</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -3140,6 +3206,9 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3171,132 +3240,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_change_log</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>메타데이터 변경 전/후 이력</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>메타데이터 필드 단위 변경 전/후 값 이력(BS_CHANGE_HISTORY는 요약)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>change_id</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -3316,29 +3392,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>변경 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>CLG-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -3354,29 +3430,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -3388,29 +3464,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>entity_type</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
@@ -3426,29 +3502,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>변경 대상 유형</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>VERSION</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>field_name</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -3464,29 +3540,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>변경 필드명</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>timeout_ms</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>before_value</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -3498,29 +3574,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>변경 전 값</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>after_value</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -3532,29 +3608,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>변경 후 값</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>changed_by</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -3570,29 +3646,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>변경자 ID</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>changed_at</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -3608,24 +3684,24 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>변경 일시</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>2026-07-30 10:00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -3642,6 +3718,9 @@
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3673,132 +3752,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_cache_event</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>다중 WAS 메타데이터 Cache 무효화 이벤트(§8.4 Registry 갱신)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -3818,29 +3904,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>캐시 이벤트 ID</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>EVT-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -3852,29 +3938,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>대상 서비스 ID(NULL=전체 무효화)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -3886,29 +3972,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>대상 버전</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>event_type</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -3924,29 +4010,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>INVALIDATE, RELOAD, EVICT_ALL  ※CHECK</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>이벤트 유형</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>INVALIDATE</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -3962,29 +4048,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>이벤트 발생 일시</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>2026-07-30 10:00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>created_by</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -4000,29 +4086,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>발생시킨 운영자 ID</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>processed_yn</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>char(1)</t>
         </is>
@@ -4038,29 +4124,29 @@
           <t>'N'</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Y(처리완료), N(미처리)</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>이벤트 처리 여부</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>processed_at</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -4072,29 +4158,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>처리 완료 일시</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>2026-07-30 10:00:05</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>server_instance</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -4106,24 +4192,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>이벤트 소비 WAS 인스턴스</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>was-02</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4140,6 +4226,9 @@
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4171,132 +4260,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>서비스 Catalog</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Business Service 마스터(서비스 존재 등록). 버전·상태 세부는 BS_SERVICE_VERSION이 담당</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -4316,29 +4412,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>서비스 고유 식별자(대문자·점 구분, 전역 유일, Handler ID와 일치). 실행/조회 조회키 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>service_name</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
@@ -4354,29 +4450,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>서비스 표시명(화면 목록/상세)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>결산 진행상태 조회</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>service_description</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>varchar(300)</t>
         </is>
@@ -4392,29 +4488,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>서비스 설명(업무 목적). CON-01 §8.3 필수 항목</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>결산 단계별 상태 조회</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>domain_code</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -4430,29 +4526,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>CLOSING, JOURNAL, EXPENSE, STATEMENT, CSM (파일럿 5개, 확장 가능)</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>업무 도메인 분류 코드(표시용)</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>CLOSING</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>service_type</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>varchar(10)</t>
         </is>
@@ -4468,29 +4564,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>READ(조회), ACTION(실행)  ※CHECK</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>서비스 성격. 등록 시 값 검증에만 사용</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>READ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>source_system</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -4506,29 +4602,29 @@
           <t>'IFRS17'</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>IFRS17 (Phase1 기본·고정, 확장 가능)</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>서비스 원천 시스템(표시용)</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>IFRS17</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>owner_department</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
@@ -4544,29 +4640,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>서비스 업무 책임 부서(Owner)</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>정보기술팀</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>active_yn</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>char(1)</t>
         </is>
@@ -4582,29 +4678,29 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>서비스 사용 여부(N이면 신규 호출 즉시 차단) [핵심 로직]</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -4620,29 +4716,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>최초 등록 일시(감사)</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>created_by</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -4658,29 +4754,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>최초 등록자 ID(감사)</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -4696,29 +4792,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>최종 수정 일시(감사)</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>2026-07-30 10:00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>updated_by</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -4734,24 +4830,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>최종 수정자 ID(감사)</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4768,6 +4864,9 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4799,132 +4898,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_version</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>service_id + version</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>서비스의 버전별 상태·Schema·Timeout·구현 Bean 정의</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -4944,29 +5050,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -4986,29 +5092,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>implementation_bean</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
@@ -5024,29 +5130,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>실행 대상 Spring Bean 명</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>closingStatusBusinessService</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>timeout_ms</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -5062,29 +5168,29 @@
           <t>30000</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>실행 타임아웃(밀리초). 초과 시 BS-SYS-504</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>request_schema</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -5096,29 +5202,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>요청 JSON 스키마 정의</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>{...}</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>response_schema</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -5130,29 +5236,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>응답 JSON 스키마 정의</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>{...}</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>status_code</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -5168,29 +5274,29 @@
           <t>'ACTIVE'</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>ACTIVE(활성), INACTIVE(비활성)</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>버전 상태(활성 버전만 실행) [핵심 로직]</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>effective_from</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -5206,29 +5312,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>버전 유효 시작 일시</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>effective_to</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -5240,24 +5346,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>버전 유효 종료 일시(NULL=무기한)</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>2027-01-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5274,6 +5380,9 @@
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5305,132 +5414,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_param</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>입력 파라미터 정의</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>service_id + version + param_name</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>서비스 버전별 입력 파라미터 명세(§8.3 요청 JSON 명세)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -5450,29 +5566,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -5492,29 +5608,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>param_name</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -5534,29 +5650,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>파라미터 명</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>closingYearMonth</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>param_type</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -5572,29 +5688,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>STRING, NUMBER, BOOLEAN, DATE 등</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>파라미터 데이터 타입</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>STRING</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>required_yn</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>char(1)</t>
         </is>
@@ -5610,29 +5726,29 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Y(필수), N(선택)</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>필수 여부</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>param_description</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>varchar(300)</t>
         </is>
@@ -5644,29 +5760,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>파라미터 설명</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>결산 년월(YYYY-MM)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>display_order</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -5682,24 +5798,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>화면 표시 순서</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5716,6 +5832,9 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5747,132 +5866,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_service_role</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>서비스 필요 권한</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>service_id + role_code</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>서비스 호출에 필요한 권한(화면ID:액션). 외부 권한API의 사용자 화면권한과 AND 비교(§6.2 권한 원칙)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규) + 권한설계 상세화</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -5892,29 +6018,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>role_code</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -5934,29 +6060,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>화면ID:액션 형식  ·  화면ID=[A-Z]{4}M[0-9]{3}  ·  액션=inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력)</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>필요 권한 코드(화면ID:액션). 외부 권한API의 사용자 화면권한(Y/N)과 AND 비교</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>CLSGM001:inqy</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -5972,29 +6098,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>등록 일시</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>created_by</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -6010,24 +6136,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>등록자 ID</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6044,6 +6170,9 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6075,132 +6204,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_client</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>호출 Client 등록</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>서비스를 호출하는 Client(채널) 등록(§5.2 X-Client-ID)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -6220,29 +6356,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>형식 {채널}-{시스템}-{일련번호}  ·  정규식 [A-Z0-9]+-[A-Z0-9]+-[0-9]{2}  ·  채널은 하이픈 없는 코드</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>호출 Client 식별자(X-Client-ID). 명명규칙 {채널}-{시스템}-{일련번호} [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>client_name</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
@@ -6258,29 +6394,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Client 명칭</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>MCP 게이트웨이 01</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>channel_type</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -6296,29 +6432,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, BATCH 등</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>호출 채널 유형</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>MCP</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>allowed_ip_cidr</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
@@ -6330,29 +6466,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>허용 IP 대역(CIDR)</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>10.0.0.0/8</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>active_yn</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>char(1)</t>
         </is>
@@ -6368,29 +6504,29 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Client 사용 여부(N이면 인증 차단) [핵심 로직]</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -6406,29 +6542,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>등록 일시</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>created_by</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -6444,24 +6580,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>등록자 ID</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6478,6 +6614,9 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6509,132 +6648,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_client_service</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>Client별 호출 허용</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>client_id + service_id</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Client가 호출 가능한 서비스 매핑(허용 목록)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -6654,29 +6800,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Client ID(FK→BS_CLIENT)</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -6696,29 +6842,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>active_yn</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>char(1)</t>
         </is>
@@ -6734,29 +6880,29 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>호출 허용 여부 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -6772,29 +6918,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>등록 일시</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>created_by</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -6810,24 +6956,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>등록자 ID</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6844,6 +6990,9 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6875,132 +7024,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_call_log</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>호출 감사로그</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>서비스 호출 감사로그(§6.3). request_id(PK)는 서버 생성 유일값, 호출자 X-Request-ID는 client_request_id에 별도 저장(무결성)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본) + 감사 무결성 보강</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -7020,29 +7176,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>호출 요청 고유 ID — 서버 생성 유일값(호출자 헤더 미사용). 코드 반영 예정 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>REQ-20260714093012345-1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>client_request_id</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -7054,29 +7210,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>[신규] 호출자 X-Request-ID 원본(추적·상관용, 유일성 미보장·중복 가능)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>REQ-20260714-0001</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>trace_id</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -7088,29 +7244,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>분산추적/장애분석용 선택 pass-through(§5.2 X-Trace-ID, 응답 에코). 운영 주 추적키는 request_id · receiver 그룹핑 로직 없음</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>TRACE-abc123</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -7126,29 +7282,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>호출 서비스 ID</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>service_version</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -7164,29 +7320,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>호출 서비스 버전</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -7202,29 +7358,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>호출 Client ID</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
@@ -7236,29 +7392,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>사용자 ID(대리호출 시 실사용자)</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>department_code</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
@@ -7270,29 +7426,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>사용자 부서 코드</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>FIN01</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>requested_at</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -7308,29 +7464,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>요청 수신 일시</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>completed_at</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -7342,29 +7498,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>처리 완료 일시</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:01</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>elapsed_ms</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -7376,29 +7532,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>처리 소요시간(ms)</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>850</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>status_code</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -7414,29 +7570,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>COMPLETED, PARTIAL, FAILED 등 (부록D)</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>처리 상태</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>http_status</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -7448,29 +7604,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>200, 400, 401, 403, 404, 500 등</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>HTTP 상태코드</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>error_code</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
@@ -7482,29 +7638,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>BS-VAL-001, BS-AUTH-003 등 (부록A)</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>오류코드</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>BS-VAL-001</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>error_id</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -7516,29 +7672,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>오류 추적 ID</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>ERR-xyz789</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>parameter_hash</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>varchar(128)</t>
         </is>
@@ -7550,29 +7706,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>요청 파라미터 Hash(원문 저장 금지)</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>a1b2c3...</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>result_count</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -7584,29 +7740,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>결과 건수</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>remote_ip</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>varchar(64)</t>
         </is>
@@ -7618,29 +7774,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>호출 원격 IP</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>10.1.2.3</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>server_instance</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -7652,24 +7808,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>처리 WAS 인스턴스</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>was-01</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -7686,6 +7842,9 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7717,132 +7876,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>business_service.bs_access_entity</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>접근 업무객체 이력</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>request_id + entity_type + entity_id</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>호출별 접근 업무객체 이력(§6.3 accessed_entity_ids)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -7862,29 +8028,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>호출 요청 ID(FK→BS_CALL_LOG)</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>REQ-20260714-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>entity_type</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
@@ -7904,29 +8070,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>접근 객체 유형</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>CLOSING</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
@@ -7946,29 +8112,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>접근 객체 식별자</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>accessed_at</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -7984,24 +8150,24 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>접근 일시</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -8018,6 +8184,9 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -7,21 +7,22 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테이블 목록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_VERSION" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_PARAM" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_ROLE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_CLIENT" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_CLIENT_SERVICE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_CALL_LOG" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_ACCESS_ENTITY" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_CHANGE_HISTORY" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_CHANNEL" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_DEPLOYMENT" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_APPROVAL" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_CHANGE_LOG" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_CACHE_EVENT" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테이블 목록" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_VERSION" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_PARAM" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_ROLE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_CLIENT" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_CLIENT_SERVICE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_CALL_LOG" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_ACCESS_ENTITY" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_CHANGE_HISTORY" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_CHANNEL" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_DEPLOYMENT" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_APPROVAL" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_CHANGE_LOG" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS_SERVICE_CACHE_EVENT" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -141,10 +142,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -152,13 +163,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -547,588 +552,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IFRS17 Business Service Layer — 테이블 목록</t>
+          <t>개정 이력 (Revision History)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>근거: 상세설계서 v1.3 §7 메타데이터 및 Database 설계 / DBMS: PostgreSQL / 스키마: business_service</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
+          <t>문서: 별첨C 테이블 설계서 (IFRS17 Business Service Layer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>버전</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>테이블 ID (영문)</t>
+          <t>개정일자</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>논리명</t>
+          <t>개정자</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>사용 여부</t>
+          <t>변경 내용</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>목적/설명</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>주요 Key (PK)</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>정의 출처</t>
+          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>BS_SERVICE</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>서비스 Catalog</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>사용</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Business Service 마스터(서비스 존재 등록). 버전·상태 세부는 BS_SERVICE_VERSION이 담당</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>service_id</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.3 (원본)</t>
-        </is>
-      </c>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>최초 작성 — 설계서 §7.2/7.3 기준 14개 테이블 설계서(테이블 목록 + 14시트)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>BS_SERVICE_VERSION</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>서비스 버전</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>사용</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>서비스의 버전별 상태·Schema·Timeout·구현 Bean 정의</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>service_id + version</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.3 (원본)</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>BS_SERVICE에 service_description 컬럼 추가</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>§7.3 DDL 누락 보완(CON-01 §8.3 필수 항목)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>BS_SERVICE_PARAM</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>입력 파라미터 정의</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>미사용</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>서비스 버전별 입력 파라미터 명세(§8.3 요청 JSON 명세)</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>service_id + version + param_name</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>테이블 목록에 사용 여부 열 추가</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>master 코드 사용 여부 조사</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>BS_SERVICE_ROLE</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>서비스 필요 권한</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>사용</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>서비스 호출에 필요한 권한(화면ID:액션). 외부 권한API의 사용자 화면권한과 AND 비교(§6.2 권한 원칙)</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>service_id + role_code</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.2 (신규) + 권한설계 상세화</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_ROLE 권한 규약 정의(role_code = 화면ID:액션)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>역할 기반 → 화면/액션 기반, 예: ICCOM123:inqy</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>BS_CLIENT</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>호출 Client 등록</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>사용</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>서비스를 호출하는 Client(채널) 등록(§5.2 X-Client-ID)</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>client_id</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>BS_CLIENT.client_id 명명 규칙 정의({채널}-{시스템}-{일련번호})</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>예: MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>BS_CLIENT_SERVICE</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Client별 호출 허용</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>사용</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Client가 호출 가능한 서비스 매핑(허용 목록)</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>client_id + service_id</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>BS_CALL_LOG 감사 무결성 보강(request_id 서버생성 + client_request_id 추가, trace_id 용도 정정)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>18→19 컬럼</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>BS_CALL_LOG</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>호출 감사로그</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>사용</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>서비스 호출 감사로그(§6.3). request_id(PK)는 서버 생성 유일값, 호출자 X-Request-ID는 client_request_id에 별도 저장(무결성)</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>request_id</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.3 (원본) + 감사 무결성 보강</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>v1.6</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>14개 테이블 사용/미사용 검토 완료 및 사용 여부 2분류 통일</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>사용 6 / 미사용 8</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>BS_ACCESS_ENTITY</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>접근 업무객체 이력</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>미사용</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>호출별 접근 업무객체 이력(§6.3 accessed_entity_ids)</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>request_id + entity_type + entity_id</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
-        </is>
-      </c>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>표 데이터 셀 배경 흰색 통일, 시트 간 하이퍼링크(양방향) 추가</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>BS_CHANGE_HISTORY</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>메타데이터 변경이력</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>미사용</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>메타데이터 변경 요약 이력(§7.4). ※코드에 recordChange 기록 로직 존재하나 운영 범위 제외(미사용)</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>change_id</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>BS_SERVICE_CHANNEL</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>서비스별 허용 채널/Client 정책</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>미사용</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>서비스 버전별 허용 채널과 Client 정책(§5.2, §6.2)</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>service_id + version + channel_code</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>BS_SERVICE_DEPLOYMENT</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>배포 구현체 정보</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>미사용</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>배포된 구현체·JAR/WAR·Bean·Checksum 정보(§8.4 배포·검증)</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>deployment_id</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>BS_SERVICE_APPROVAL</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>등록·변경·활성화 승인 이력</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>미사용</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>서비스 등록·변경·활성화 승인 이력(§6.2 운영자 승인, §8.4)</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>approval_id</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>BS_SERVICE_CHANGE_LOG</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>메타데이터 변경 전/후 이력</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>미사용</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>메타데이터 필드 단위 변경 전/후 값 이력(BS_CHANGE_HISTORY는 요약)</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>change_id</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>BS_SERVICE_CACHE_EVENT</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>다중 WAS Cache 무효화 이벤트</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>미사용</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>다중 WAS 메타데이터 Cache 무효화 이벤트(§8.4 Registry 갱신)</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>event_id</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>사용 여부 범례: 사용=Phase1 코드에서 실제 사용(6개) · 미사용=Phase1 미사용(8개, 정의만/범위제외/미구현 등 향후 확장·예약 포함)</t>
-        </is>
-      </c>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>v1.8</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>개정이력 시트 추가</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1139,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1155,144 +865,144 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>테이블 설계서 — BS_CHANGE_HISTORY</t>
+          <t>테이블 설계서 — BS_ACCESS_ENTITY</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>business_service.bs_change_history</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>business_service.bs_access_entity</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
-        <is>
-          <t>메타데이터 변경이력</t>
-        </is>
-      </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>접근 업무객체 이력</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>change_id</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>request_id + entity_type + entity_id</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>메타데이터 변경 요약 이력(§7.4). ※코드에 recordChange 기록 로직 존재하나 운영 범위 제외(미사용)</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>호출별 접근 업무객체 이력(§6.3 accessed_entity_ids)</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>◀ 테이블 목록</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>change_id</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>request_id</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -1312,34 +1022,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>변경 이력 ID</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>CHG-0001</t>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>호출 요청 ID(FK→BS_CALL_LOG)</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>REQ-20260714-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>entity_type</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1350,34 +1064,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>SERVICE, VERSION, PARAM, ROLE, CLIENT 등</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>변경 대상 유형</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>접근 객체 유형</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>CLOSING</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1388,31 +1106,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>변경 대상 식별자</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>IFRS17.CLOSING.STATUS</t>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>접근 객체 식별자</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>change_type</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>accessed_at</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -1423,137 +1141,27 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>CREATE, UPDATE, DELETE, ACTIVATE, DEACTIVATE  ※CHECK</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>변경 유형</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>UPDATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>changed_by</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>varchar(30)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>변경자 ID</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>E12345</t>
+          <t>current_timestamp</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>접근 일시</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>changed_at</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>current_timestamp</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>변경 일시</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-30 10:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>change_summary</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>varchar(500)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>변경 요약</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>timeout_ms 30000→60000</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -1561,9 +1169,9 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A12:H12"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="A15:H15"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B2:E2"/>
@@ -1599,146 +1207,146 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>테이블 설계서 — BS_SERVICE_CHANNEL</t>
+          <t>테이블 설계서 — BS_CHANGE_HISTORY</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>business_service.bs_service_channel</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>business_service.bs_change_history</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
-        <is>
-          <t>서비스별 허용 채널/Client 정책</t>
-        </is>
-      </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>메타데이터 변경이력</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>service_id + version + channel_code</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>change_id</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>서비스 버전별 허용 채널과 Client 정책(§5.2, §6.2)</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>메타데이터 변경 요약 이력(§7.4). ※코드에 recordChange 기록 로직 존재하나 운영 범위 제외(미사용)</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>◀ 테이블 목록</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>service_id</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>varchar(100)</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>change_id</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>varchar(80)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1756,115 +1364,107 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>변경 이력 ID</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>CHG-0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>entity_type</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>SERVICE, VERSION, PARAM, ROLE, CLIENT 등</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>변경 대상 유형</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>SERVICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>entity_id</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>변경 대상 식별자</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>change_type</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>서비스 버전(FK)</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>channel_code</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>varchar(30)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>MCP, AI-AGENT, INTERNAL 등</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>허용 채널 코드</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>MCP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>allow_yn</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>char(1)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -1875,34 +1475,34 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>'Y'</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Y(허용), N(차단)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>채널 허용 여부</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>CREATE, UPDATE, DELETE, ACTIVATE, DEACTIVATE  ※CHECK</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>변경 유형</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>UPDATE</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>client_policy</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -1913,32 +1513,32 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>'ALLOWLIST'</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>ALLOWLIST, DENYLIST, OPEN  ※CHECK</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Client 접근 정책</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>ALLOWLIST</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>변경자 ID</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>changed_at</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -1954,62 +1554,58 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>등록 일시</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-14 09:00:00</t>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>변경 일시</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30 10:00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>varchar(30)</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>change_summary</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>varchar(500)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>등록자 ID</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>E12345</t>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>변경 요약</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>timeout_ms 30000→60000</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -2039,6 +1635,462 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>테이블 설계서 — BS_SERVICE_CHANNEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>테이블 ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>business_service.bs_service_channel</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>논리명</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>서비스별 허용 채널/Client 정책</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>주요 Key</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>service_id + version + channel_code</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>DBMS</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>PostgreSQL</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>서비스 버전별 허용 채널과 Client 정책(§5.2, §6.2)</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.2 (신규)</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>컬럼 ID</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Not Null</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>유효값(코드값)</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>용도</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>service_id</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>IFRS17.CLOSING.STATUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>서비스 버전(FK)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>channel_code</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>MCP, AI-AGENT, INTERNAL 등</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>허용 채널 코드</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>allow_yn</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>char(1)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>'Y'</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Y(허용), N(차단)</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>채널 허용 여부</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>client_policy</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>'ALLOWLIST'</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>ALLOWLIST, DENYLIST, OPEN  ※CHECK</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Client 접근 정책</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>ALLOWLIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>current_timestamp</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>등록 일시</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>등록자 ID</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>E12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="G3:H3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2060,139 +2112,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_deployment</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>배포 구현체 정보</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>배포된 구현체·JAR/WAR·Bean·Checksum 정보(§8.4 배포·검증)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>◀ 테이블 목록</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>deployment_id</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -2212,29 +2264,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>배포 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>DEP-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -2250,29 +2302,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -2288,29 +2340,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>implementation_bean</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
@@ -2326,29 +2378,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>배포된 Spring Bean 명</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>closingStatusBusinessService</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>artifact_type</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>varchar(10)</t>
         </is>
@@ -2364,29 +2416,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>JAR, WAR  ※CHECK</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>배포 산출물 유형</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>JAR</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>artifact_name</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
@@ -2402,29 +2454,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>배포 산출물 파일명</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>bsl-closing-1.0.jar</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>checksum</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>varchar(128)</t>
         </is>
@@ -2440,29 +2492,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>산출물 무결성 체크섬(SHA-256 등)</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>9f86d0...</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>deploy_status</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -2478,29 +2530,29 @@
           <t>'DEPLOYED'</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>DEPLOYED, VERIFIED, FAILED, RETIRED  ※CHECK</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>배포 상태</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>DEPLOYED</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>bean_verified_yn</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>char(1)</t>
         </is>
@@ -2516,29 +2568,29 @@
           <t>'N'</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Y(검증완료), N(미검증)</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Bean 존재·Interface 검증 여부(§8.4)</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>deployed_by</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -2554,29 +2606,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>배포자 ID</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>deployed_at</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -2592,29 +2644,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>배포 일시</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>2026-07-14 08:00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>server_instance</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -2626,24 +2678,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>배포 대상 WAS 인스턴스</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>was-01</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -2667,7 +2719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2694,139 +2746,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_approval</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>등록·변경·활성화 승인 이력</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스 등록·변경·활성화 승인 이력(§6.2 운영자 승인, §8.4)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>◀ 테이블 목록</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>approval_id</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -2846,29 +2898,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>승인 이력 ID</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>APR-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -2884,29 +2936,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -2918,29 +2970,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>request_type</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -2956,29 +3008,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>REGISTER, MODIFY, ACTIVATE, DEACTIVATE  ※CHECK</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>승인 요청 유형</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>REGISTER</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>approval_status</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -2994,29 +3046,29 @@
           <t>'REQUESTED'</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>REQUESTED, APPROVED, REJECTED  ※CHECK</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>승인 상태</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>requested_by</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -3032,29 +3084,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>요청자 ID</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>requested_at</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -3070,29 +3122,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>요청 일시</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>2026-07-14 08:30:00</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -3104,29 +3156,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>승인자 ID</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>E67890</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>approved_at</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -3138,29 +3190,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>승인 일시</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>approval_comment</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>varchar(500)</t>
         </is>
@@ -3172,24 +3224,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>승인/반려 사유</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>최초 등록 승인</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -3205,518 +3257,6 @@
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G3:H3"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>테이블 설계서 — BS_SERVICE_CHANGE_LOG</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>테이블 ID</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>business_service.bs_service_change_log</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>논리명</t>
-        </is>
-      </c>
-      <c r="G2" s="11" t="inlineStr">
-        <is>
-          <t>메타데이터 변경 전/후 이력</t>
-        </is>
-      </c>
-      <c r="H2" s="11" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>주요 Key</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>change_id</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>DBMS</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>PostgreSQL</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>메타데이터 필드 단위 변경 전/후 값 이력(BS_CHANGE_HISTORY는 요약)</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>출처</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>◀ 테이블 목록</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>컬럼 ID</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>타입</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Not Null</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>유효값(코드값)</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>용도</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>change_id</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>varchar(80)</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>변경 이력 ID</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>CLG-0001</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>service_id</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>varchar(100)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>서비스 ID(FK→BS_SERVICE)</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>IFRS17.CLOSING.STATUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>서비스 버전</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>entity_type</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>varchar(50)</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>변경 대상 유형</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>VERSION</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>field_name</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>varchar(100)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>변경 필드명</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>timeout_ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>before_value</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>변경 전 값</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>after_value</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>변경 후 값</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>60000</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>changed_by</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>varchar(30)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>변경자 ID</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>E12345</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>changed_at</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>current_timestamp</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>변경 일시</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-30 10:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
@@ -3747,144 +3287,656 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>테이블 설계서 — BS_SERVICE_CHANGE_LOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>테이블 ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>business_service.bs_service_change_log</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>논리명</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>메타데이터 변경 전/후 이력</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>주요 Key</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>change_id</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>DBMS</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>PostgreSQL</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>메타데이터 필드 단위 변경 전/후 값 이력(BS_CHANGE_HISTORY는 요약)</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.2 (신규)</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>컬럼 ID</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Not Null</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>유효값(코드값)</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>용도</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>change_id</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>varchar(80)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>변경 이력 ID</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>CLG-0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>service_id</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>서비스 ID(FK→BS_SERVICE)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>IFRS17.CLOSING.STATUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>서비스 버전</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>entity_type</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>변경 대상 유형</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>VERSION</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>field_name</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>변경 필드명</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>timeout_ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>before_value</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>변경 전 값</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>after_value</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>변경 후 값</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>변경자 ID</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>E12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>changed_at</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>current_timestamp</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>변경 일시</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>테이블 설계서 — BS_SERVICE_CACHE_EVENT</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_cache_event</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>다중 WAS Cache 무효화 이벤트</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>다중 WAS 메타데이터 Cache 무효화 이벤트(§8.4 Registry 갱신)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>◀ 테이블 목록</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -3904,29 +3956,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>캐시 이벤트 ID</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>EVT-0001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -3938,29 +3990,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>대상 서비스 ID(NULL=전체 무효화)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -3972,29 +4024,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>대상 버전</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>event_type</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -4010,29 +4062,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>INVALIDATE, RELOAD, EVICT_ALL  ※CHECK</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>이벤트 유형</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>INVALIDATE</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -4048,29 +4100,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>이벤트 발생 일시</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>2026-07-30 10:00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>created_by</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -4086,29 +4138,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>발생시킨 운영자 ID</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>processed_yn</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>char(1)</t>
         </is>
@@ -4124,29 +4176,29 @@
           <t>'N'</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Y(처리완료), N(미처리)</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>이벤트 처리 여부</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>processed_at</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -4158,29 +4210,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>처리 완료 일시</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>2026-07-30 10:00:05</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>server_instance</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -4192,24 +4244,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>이벤트 소비 WAS 인스턴스</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>was-02</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4239,6 +4291,598 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>IFRS17 Business Service Layer — 테이블 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>근거: 상세설계서 v1.3 §7 메타데이터 및 Database 설계 / DBMS: PostgreSQL / 스키마: business_service</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>테이블 ID (영문)</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>논리명</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>사용 여부</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>목적/설명</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>주요 Key (PK)</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>정의 출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>BS_SERVICE</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>서비스 Catalog</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Business Service 마스터(서비스 존재 등록). 버전·상태 세부는 BS_SERVICE_VERSION이 담당</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>service_id</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.3 (원본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_VERSION</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>서비스 버전</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>서비스의 버전별 상태·Schema·Timeout·구현 Bean 정의</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>service_id + version</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.3 (원본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_PARAM</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>입력 파라미터 정의</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>서비스 버전별 입력 파라미터 명세(§8.3 요청 JSON 명세)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>service_id + version + param_name</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.2 (신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_ROLE</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>서비스 필요 권한</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>서비스 호출에 필요한 권한(화면ID:액션). 외부 권한API의 사용자 화면권한과 AND 비교(§6.2 권한 원칙)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>service_id + role_code</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.2 (신규) + 권한설계 상세화</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>BS_CLIENT</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>호출 Client 등록</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>서비스를 호출하는 Client(채널) 등록(§5.2 X-Client-ID)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>client_id</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.2 (신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>BS_CLIENT_SERVICE</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Client별 호출 허용</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Client가 호출 가능한 서비스 매핑(허용 목록)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>client_id + service_id</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.2 (신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>BS_CALL_LOG</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>호출 감사로그</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>서비스 호출 감사로그(§6.3). request_id(PK)는 서버 생성 유일값, 호출자 X-Request-ID는 client_request_id에 별도 저장(무결성)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>request_id</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.3 (원본) + 감사 무결성 보강</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>BS_ACCESS_ENTITY</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>접근 업무객체 이력</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>호출별 접근 업무객체 이력(§6.3 accessed_entity_ids)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>request_id + entity_type + entity_id</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.2 (신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>BS_CHANGE_HISTORY</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>메타데이터 변경이력</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>메타데이터 변경 요약 이력(§7.4). ※코드에 recordChange 기록 로직 존재하나 운영 범위 제외(미사용)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>change_id</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.2 (신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_CHANNEL</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>서비스별 허용 채널/Client 정책</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>서비스 버전별 허용 채널과 Client 정책(§5.2, §6.2)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>service_id + version + channel_code</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.2 (신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_DEPLOYMENT</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>배포 구현체 정보</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>배포된 구현체·JAR/WAR·Bean·Checksum 정보(§8.4 배포·검증)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>deployment_id</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.2 (신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_APPROVAL</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>등록·변경·활성화 승인 이력</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>서비스 등록·변경·활성화 승인 이력(§6.2 운영자 승인, §8.4)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>approval_id</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.2 (신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_CHANGE_LOG</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>메타데이터 변경 전/후 이력</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>메타데이터 필드 단위 변경 전/후 값 이력(BS_CHANGE_HISTORY는 요약)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>change_id</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.2 (신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_CACHE_EVENT</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>다중 WAS Cache 무효화 이벤트</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>다중 WAS 메타데이터 Cache 무효화 이벤트(§8.4 Registry 갱신)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.2 (신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>사용 여부 범례: 사용=Phase1 코드에서 실제 사용(6개) · 미사용=Phase1 미사용(8개, 정의만/범위제외/미구현 등 향후 확장·예약 포함)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4260,139 +4904,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>서비스 Catalog</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Business Service 마스터(서비스 존재 등록). 버전·상태 세부는 BS_SERVICE_VERSION이 담당</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>◀ 테이블 목록</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -4412,29 +5056,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>서비스 고유 식별자(대문자·점 구분, 전역 유일, Handler ID와 일치). 실행/조회 조회키 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>service_name</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
@@ -4450,29 +5094,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>서비스 표시명(화면 목록/상세)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>결산 진행상태 조회</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>service_description</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>varchar(300)</t>
         </is>
@@ -4488,29 +5132,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>서비스 설명(업무 목적). CON-01 §8.3 필수 항목</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>결산 단계별 상태 조회</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>domain_code</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -4526,29 +5170,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>CLOSING, JOURNAL, EXPENSE, STATEMENT, CSM (파일럿 5개, 확장 가능)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>업무 도메인 분류 코드(표시용)</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>CLOSING</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>service_type</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>varchar(10)</t>
         </is>
@@ -4564,29 +5208,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>READ(조회), ACTION(실행)  ※CHECK</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>서비스 성격. 등록 시 값 검증에만 사용</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>READ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>source_system</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -4602,29 +5246,29 @@
           <t>'IFRS17'</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>IFRS17 (Phase1 기본·고정, 확장 가능)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>서비스 원천 시스템(표시용)</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>IFRS17</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>owner_department</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
@@ -4640,29 +5284,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>서비스 업무 책임 부서(Owner)</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>정보기술팀</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>active_yn</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>char(1)</t>
         </is>
@@ -4678,29 +5322,29 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>서비스 사용 여부(N이면 신규 호출 즉시 차단) [핵심 로직]</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -4716,29 +5360,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>최초 등록 일시(감사)</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>created_by</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -4754,29 +5398,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>최초 등록자 ID(감사)</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -4792,29 +5436,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>최종 수정 일시(감사)</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>2026-07-30 10:00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>updated_by</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -4830,24 +5474,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>최종 수정자 ID(감사)</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -4871,7 +5515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4898,139 +5542,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_version</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>service_id + version</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스의 버전별 상태·Schema·Timeout·구현 Bean 정의</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>◀ 테이블 목록</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -5050,29 +5694,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -5092,29 +5736,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>서비스 버전</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>implementation_bean</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
@@ -5130,29 +5774,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>실행 대상 Spring Bean 명</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>closingStatusBusinessService</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>timeout_ms</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -5168,29 +5812,29 @@
           <t>30000</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>실행 타임아웃(밀리초). 초과 시 BS-SYS-504</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>request_schema</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -5202,29 +5846,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>요청 JSON 스키마 정의</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>{...}</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>response_schema</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -5236,29 +5880,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>응답 JSON 스키마 정의</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>{...}</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>status_code</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -5274,29 +5918,29 @@
           <t>'ACTIVE'</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>ACTIVE(활성), INACTIVE(비활성)</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>버전 상태(활성 버전만 실행) [핵심 로직]</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>effective_from</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -5312,29 +5956,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>버전 유효 시작 일시</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>effective_to</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -5346,24 +5990,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>버전 유효 종료 일시(NULL=무기한)</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>2027-01-01 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5387,7 +6031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5414,139 +6058,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_param</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>입력 파라미터 정의</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>service_id + version + param_name</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스 버전별 입력 파라미터 명세(§8.3 요청 JSON 명세)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>◀ 테이블 목록</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -5566,29 +6210,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE_VERSION)</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -5608,29 +6252,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>서비스 버전(FK)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>param_name</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -5650,29 +6294,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>파라미터 명</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>closingYearMonth</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>param_type</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -5688,29 +6332,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>STRING, NUMBER, BOOLEAN, DATE 등</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>파라미터 데이터 타입</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>STRING</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>required_yn</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>char(1)</t>
         </is>
@@ -5726,29 +6370,29 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Y(필수), N(선택)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>필수 여부</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>param_description</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>varchar(300)</t>
         </is>
@@ -5760,29 +6404,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>파라미터 설명</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>결산 년월(YYYY-MM)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>display_order</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -5798,24 +6442,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>화면 표시 순서</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5839,7 +6483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5866,139 +6510,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_service_role</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>서비스 필요 권한</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>service_id + role_code</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스 호출에 필요한 권한(화면ID:액션). 외부 권한API의 사용자 화면권한과 AND 비교(§6.2 권한 원칙)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규) + 권한설계 상세화</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>◀ 테이블 목록</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -6018,29 +6662,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>role_code</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -6060,29 +6704,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>화면ID:액션 형식  ·  화면ID=[A-Z]{4}M[0-9]{3}  ·  액션=inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력)</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>필요 권한 코드(화면ID:액션). 외부 권한API의 사용자 화면권한(Y/N)과 AND 비교</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>CLSGM001:inqy</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -6098,29 +6742,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>등록 일시</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>created_by</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -6136,24 +6780,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>등록자 ID</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6177,7 +6821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6204,139 +6848,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_client</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>호출 Client 등록</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스를 호출하는 Client(채널) 등록(§5.2 X-Client-ID)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>◀ 테이블 목록</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -6356,29 +7000,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>형식 {채널}-{시스템}-{일련번호}  ·  정규식 [A-Z0-9]+-[A-Z0-9]+-[0-9]{2}  ·  채널은 하이픈 없는 코드</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>호출 Client 식별자(X-Client-ID). 명명규칙 {채널}-{시스템}-{일련번호} [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>client_name</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
@@ -6394,29 +7038,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Client 명칭</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>MCP 게이트웨이 01</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>channel_type</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -6432,29 +7076,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>MCP, AI-AGENT, BATCH 등</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>호출 채널 유형</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>MCP</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>allowed_ip_cidr</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
@@ -6466,29 +7110,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>허용 IP 대역(CIDR)</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>10.0.0.0/8</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>active_yn</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>char(1)</t>
         </is>
@@ -6504,29 +7148,29 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Y(사용), N(미사용)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Client 사용 여부(N이면 인증 차단) [핵심 로직]</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -6542,29 +7186,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>등록 일시</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>created_by</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -6580,24 +7224,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>등록자 ID</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6621,7 +7265,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6648,139 +7292,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_client_service</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>Client별 호출 허용</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>client_id + service_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Client가 호출 가능한 서비스 매핑(허용 목록)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>◀ 테이블 목록</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -6800,29 +7444,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Client ID(FK→BS_CLIENT)</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -6842,29 +7486,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>active_yn</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>char(1)</t>
         </is>
@@ -6880,29 +7524,29 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Y(허용), N(차단)</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>호출 허용 여부 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -6918,29 +7562,29 @@
           <t>current_timestamp</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>등록 일시</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>created_by</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
@@ -6956,24 +7600,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>등록자 ID</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6997,7 +7641,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7024,139 +7668,139 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>테이블 ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>business_service.bs_call_log</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>호출 감사로그</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>주요 Key</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>서비스 호출 감사로그(§6.3). request_id(PK)는 서버 생성 유일값, 호출자 X-Request-ID는 client_request_id에 별도 저장(무결성)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.3 (원본) + 감사 무결성 보강</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>◀ 테이블 목록</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>컬럼 ID</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>타입</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Not Null</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>유효값(코드값)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -7176,29 +7820,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>호출 요청 고유 ID — 서버 생성 유일값(호출자 헤더 미사용). 코드 반영 예정 [핵심 로직]</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>REQ-20260714093012345-1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>client_request_id</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -7210,29 +7854,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>[신규] 호출자 X-Request-ID 원본(추적·상관용, 유일성 미보장·중복 가능)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>REQ-20260714-0001</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>trace_id</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -7244,29 +7888,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>분산추적/장애분석용 선택 pass-through(§5.2 X-Trace-ID, 응답 에코). 운영 주 추적키는 request_id · receiver 그룹핑 로직 없음</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>TRACE-abc123</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>service_id</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -7282,29 +7926,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>호출 서비스 ID</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>service_version</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -7320,29 +7964,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>호출 서비스 버전</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -7358,29 +8002,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>호출 Client ID</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
@@ -7392,29 +8036,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>사용자 ID(대리호출 시 실사용자)</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>department_code</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
@@ -7426,29 +8070,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>사용자 부서 코드</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>FIN01</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>requested_at</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -7464,29 +8108,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>요청 수신 일시</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>completed_at</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -7498,29 +8142,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>처리 완료 일시</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:01</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>elapsed_ms</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -7532,29 +8176,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>처리 소요시간(ms)</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>850</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>status_code</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
@@ -7570,29 +8214,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>COMPLETED, PARTIAL, FAILED 등 (부록D)</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>처리 상태</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>http_status</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -7604,29 +8248,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>200, 400, 401, 403, 404, 500 등</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>HTTP 상태코드</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>error_code</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>varchar(50)</t>
         </is>
@@ -7638,29 +8282,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>BS-VAL-001, BS-AUTH-003 등 (부록A)</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>오류코드</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>BS-VAL-001</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>error_id</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
@@ -7672,29 +8316,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>오류 추적 ID</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>ERR-xyz789</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>parameter_hash</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>varchar(128)</t>
         </is>
@@ -7706,29 +8350,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>요청 파라미터 Hash(원문 저장 금지)</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>a1b2c3...</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>result_count</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -7740,29 +8384,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>결과 건수</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>remote_ip</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>varchar(64)</t>
         </is>
@@ -7774,29 +8418,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>호출 원격 IP</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>10.1.2.3</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>server_instance</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
@@ -7808,24 +8452,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>처리 WAS 인스턴스</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>was-01</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -7847,346 +8491,4 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>테이블 설계서 — BS_ACCESS_ENTITY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>테이블 ID</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>business_service.bs_access_entity</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>논리명</t>
-        </is>
-      </c>
-      <c r="G2" s="11" t="inlineStr">
-        <is>
-          <t>접근 업무객체 이력</t>
-        </is>
-      </c>
-      <c r="H2" s="11" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>주요 Key</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>request_id + entity_type + entity_id</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>DBMS</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>PostgreSQL</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>호출별 접근 업무객체 이력(§6.3 accessed_entity_ids)</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>출처</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>◀ 테이블 목록</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>컬럼 ID</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>타입</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Not Null</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>유효값(코드값)</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>용도</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>request_id</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>varchar(80)</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>호출 요청 ID(FK→BS_CALL_LOG)</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>REQ-20260714-0001</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>entity_type</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>varchar(50)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>접근 객체 유형</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>CLOSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>entity_id</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>varchar(200)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>접근 객체 식별자</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>accessed_at</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>current_timestamp</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>접근 일시</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-14 09:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="G3:H3"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -611,7 +611,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -621,10 +621,14 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>최초 작성 — 설계서 §7.2/7.3 기준 14개 테이블 설계서(테이블 목록 + 14시트)</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr"/>
+          <t>최초 작성 — 설계서 §7.2/7.3 기준 14개 테이블 통합 설계서(15시트). BS_SERVICE에 service_description 추가, 테이블 목록에 사용 여부 열 추가</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>schema.sql DDL 확정 포함</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -634,7 +638,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -644,12 +648,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>BS_SERVICE에 service_description 컬럼 추가</t>
+          <t>BS_SERVICE_ROLE 권한 규약 정의(role_code = 화면ID:액션)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>§7.3 DDL 누락 보완(CON-01 §8.3 필수 항목)</t>
+          <t>역할 기반 → 화면/액션 기반, 예: ICCOM123:inqy</t>
         </is>
       </c>
     </row>
@@ -661,7 +665,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -671,12 +675,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>테이블 목록에 사용 여부 열 추가</t>
+          <t>BS_CLIENT.client_id 명명 규칙 정의({채널}-{시스템}-{일련번호})</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>master 코드 사용 여부 조사</t>
+          <t>예: MCP-IFRS17-01</t>
         </is>
       </c>
     </row>
@@ -698,141 +702,14 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>BS_SERVICE_ROLE 권한 규약 정의(role_code = 화면ID:액션)</t>
+          <t>14개 테이블 사용/미사용 검토·확정, BS_CALL_LOG 감사 무결성 보강(request_id 서버생성 + client_request_id), 사용 여부 2분류, 표 배경 흰색·시트 하이퍼링크·개정이력 시트 추가</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>역할 기반 → 화면/액션 기반, 예: ICCOM123:inqy</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>v1.4</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>DBInc</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>BS_CLIENT.client_id 명명 규칙 정의({채널}-{시스템}-{일련번호})</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>예: MCP-IFRS17-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>v1.5</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>DBInc</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>BS_CALL_LOG 감사 무결성 보강(request_id 서버생성 + client_request_id 추가, trace_id 용도 정정)</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>18→19 컬럼</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>v1.6</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>DBInc</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>14개 테이블 사용/미사용 검토 완료 및 사용 여부 2분류 통일</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
           <t>사용 6 / 미사용 8</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>v1.7</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>DBInc</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>표 데이터 셀 배경 흰색 통일, 시트 간 하이퍼링크(양방향) 추가</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>v1.8</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>DBInc</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>개정이력 시트 추가</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -708,6 +708,33 @@
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>사용 6 / 미사용 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>BS_SERVICE domain_code·owner_department NOT NULL 제거(nullable)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>로직 미사용·표시용 컬럼 완화</t>
         </is>
       </c>
     </row>
@@ -5037,11 +5064,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -5054,7 +5077,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>업무 도메인 분류 코드(표시용)</t>
+          <t>업무 도메인 분류 코드(표시용, 로직 미사용). nullable</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -5092,7 +5115,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>서비스 성격. 등록 시 값 검증에만 사용</t>
+          <t>서비스 성격. 등록 시 값 검증(CON-01 필수 입력)</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -5151,11 +5174,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -5168,7 +5187,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>서비스 업무 책임 부서(Owner)</t>
+          <t>서비스 업무 책임 부서(Owner, 표시용). nullable</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">

--- a/docs/별첨C_테이블설계서.xlsx
+++ b/docs/별첨C_테이블설계서.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -735,6 +735,33 @@
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>로직 미사용·표시용 컬럼 완화</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>감사 컬럼 보강 — BS_SERVICE_VERSION(created/updated 4개), BS_SERVICE_ROLE·BS_CLIENT·BS_CLIENT_SERVICE(updated_at/by)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>생성/수정 시점 추적 일관화(BS_CALL_LOG 제외)</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5902,8 +5929,160 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>current_timestamp</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>등록 일시(감사)</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:00:00</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>등록자 ID(감사)</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>E12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>current_timestamp</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>수정 일시(감사)</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>updated_by</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>수정자 ID(감사)</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>E12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -5912,13 +6091,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A21:H21"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
@@ -6385,7 +6564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6645,7 +6824,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>등록 일시</t>
+          <t>등록 일시(감사)</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -6683,7 +6862,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>등록자 ID</t>
+          <t>등록자 ID(감사)</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -6692,8 +6871,84 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>current_timestamp</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>수정 일시(감사)</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30 10:00:00</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>updated_by</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>수정자 ID(감사)</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>E12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
         </is>
@@ -6701,10 +6956,10 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A12:H12"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="A1:H1"/>
@@ -6718,6 +6973,526 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>테이블 설계서 — BS_CLIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>테이블 ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>business_service.bs_client</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>논리명</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>호출 Client 등록</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>주요 Key</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>client_id</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>DBMS</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>PostgreSQL</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>서비스를 호출하는 Client(채널) 등록(§5.2 X-Client-ID)</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>상세설계서 v1.3 §7.2 (신규)</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>◀ 테이블 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>컬럼 ID</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Not Null</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>유효값(코드값)</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>용도</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>client_id</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>varchar(80)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>형식 {채널}-{시스템}-{일련번호}  ·  정규식 [A-Z0-9]+-[A-Z0-9]+-[0-9]{2}  ·  채널은 하이픈 없는 코드</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>호출 Client 식별자(X-Client-ID). 명명규칙 {채널}-{시스템}-{일련번호} [핵심 로직]</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>MCP-IFRS17-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>client_name</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Client 명칭</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>MCP 게이트웨이 01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>channel_type</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>MCP, AI-AGENT, BATCH 등</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>호출 채널 유형</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>allowed_ip_cidr</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>허용 IP 대역(CIDR)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.0/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>active_yn</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>char(1)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>'Y'</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Y(사용), N(미사용)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Client 사용 여부(N이면 인증 차단) [핵심 로직]</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>current_timestamp</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>등록 일시(감사)</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>등록자 ID(감사)</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>E12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>current_timestamp</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>수정 일시(감사)</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>updated_by</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>수정자 ID(감사)</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>E12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6739,7 +7514,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>테이블 설계서 — BS_CLIENT</t>
+          <t>테이블 설계서 — BS_CLIENT_SERVICE</t>
         </is>
       </c>
     </row>
@@ -6751,7 +7526,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>business_service.bs_client</t>
+          <t>business_service.bs_client_service</t>
         </is>
       </c>
       <c r="C2" s="13" t="n"/>
@@ -6764,7 +7539,7 @@
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>호출 Client 등록</t>
+          <t>Client별 호출 허용</t>
         </is>
       </c>
       <c r="H2" s="13" t="n"/>
@@ -6777,7 +7552,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>client_id</t>
+          <t>client_id + service_id</t>
         </is>
       </c>
       <c r="C3" s="13" t="n"/>
@@ -6803,7 +7578,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>서비스를 호출하는 Client(채널) 등록(§5.2 X-Client-ID)</t>
+          <t>Client가 호출 가능한 서비스 매핑(허용 목록)</t>
         </is>
       </c>
       <c r="C4" s="13" t="n"/>
@@ -6898,12 +7673,12 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>형식 {채널}-{시스템}-{일련번호}  ·  정규식 [A-Z0-9]+-[A-Z0-9]+-[0-9]{2}  ·  채널은 하이픈 없는 코드</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>호출 Client 식별자(X-Client-ID). 명명규칙 {채널}-{시스템}-{일련번호} [핵심 로직]</t>
+          <t>Client ID(FK→BS_CLIENT)</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -6915,15 +7690,19 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>client_name</t>
+          <t>service_id</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>varchar(200)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6941,24 +7720,24 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Client 명칭</t>
+          <t>서비스 ID(FK→BS_SERVICE)</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>MCP 게이트웨이 01</t>
+          <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>channel_type</t>
+          <t>active_yn</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>char(1)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -6969,41 +7748,45 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>'Y'</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>MCP, AI-AGENT, BATCH 등</t>
+          <t>Y(허용), N(차단)</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>호출 채널 유형</t>
+          <t>호출 허용 여부 [핵심 로직]</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>MCP</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>allowed_ip_cidr</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>current_timestamp</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -7013,24 +7796,24 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>허용 IP 대역(CIDR)</t>
+          <t>등록 일시(감사)</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>10.0.0.0/8</t>
+          <t>2026-07-14 09:00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>active_yn</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>char(1)</t>
+          <t>varchar(30)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -7041,29 +7824,29 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>'Y'</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Y(사용), N(미사용)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Client 사용 여부(N이면 인증 차단) [핵심 로직]</t>
+          <t>등록자 ID(감사)</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -7089,19 +7872,19 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>등록 일시</t>
+          <t>수정 일시(감사)</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14 09:00:00</t>
+          <t>2026-07-30 10:00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -7127,7 +7910,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>등록자 ID</t>
+          <t>수정자 ID(감사)</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -7149,382 +7932,6 @@
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="G3:H3"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>테이블 설계서 — BS_CLIENT_SERVICE</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>테이블 ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>business_service.bs_client_service</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>논리명</t>
-        </is>
-      </c>
-      <c r="G2" s="13" t="inlineStr">
-        <is>
-          <t>Client별 호출 허용</t>
-        </is>
-      </c>
-      <c r="H2" s="13" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>주요 Key</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>client_id + service_id</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>DBMS</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>PostgreSQL</t>
-        </is>
-      </c>
-      <c r="H3" s="13" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Client가 호출 가능한 서비스 매핑(허용 목록)</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>출처</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>상세설계서 v1.3 §7.2 (신규)</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>◀ 테이블 목록</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>컬럼 ID</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>타입</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>Not Null</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>유효값(코드값)</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>용도</t>
-        </is>
-      </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>client_id</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>varchar(80)</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Client ID(FK→BS_CLIENT)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>MCP-IFRS17-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>service_id</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>varchar(100)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>서비스 ID(FK→BS_SERVICE)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>IFRS17.CLOSING.STATUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>active_yn</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>char(1)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>'Y'</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Y(허용), N(차단)</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>호출 허용 여부 [핵심 로직]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>current_timestamp</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>등록 일시</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-14 09:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>varchar(30)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>등록자 ID</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>E12345</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>범례: 유효값(코드값) 열=코드성 컬럼만 기재 · PK=🔑(PK 열 Y) · [핵심 로직]=실행/조회 분기에 사용 · '-'=자유값/해당없음</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A13:H13"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="A1:H1"/>
